--- a/research/traditional_assets/database/data/argentina/argentina_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_drugs_pharmaceutical.xlsx
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1528,22 +1528,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2257424665806637</v>
+        <v>0.2249816179476314</v>
       </c>
       <c r="C2">
-        <v>6.53247437540615</v>
+        <v>6.491796957947872</v>
       </c>
       <c r="D2">
-        <v>5.70447437540615</v>
+        <v>5.728696957947871</v>
       </c>
       <c r="E2">
-        <v>-1.45</v>
+        <v>-1.3851</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0649</v>
       </c>
       <c r="G2">
         <v>0.828</v>
@@ -1564,28 +1564,28 @@
         <v>1.71</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00326447</v>
       </c>
       <c r="N2">
-        <v>1.71</v>
+        <v>1.70673553</v>
       </c>
       <c r="O2">
-        <v>0.5984999999999999</v>
+        <v>0.5973574355</v>
       </c>
       <c r="P2">
-        <v>1.1115</v>
+        <v>1.1093780945</v>
       </c>
       <c r="Q2">
-        <v>1.2015</v>
+        <v>1.1993780945</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2257424665806637</v>
+        <v>0.2269239070178095</v>
       </c>
       <c r="T2">
-        <v>0.884124310228629</v>
+        <v>0.8899291668109383</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>523.8216310764076</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2249816179476314</v>
+        <v>0.2242207693145991</v>
       </c>
       <c r="C3">
-        <v>6.491796957947872</v>
+        <v>6.451326127636213</v>
       </c>
       <c r="D3">
-        <v>5.728696957947871</v>
+        <v>5.753126127636214</v>
       </c>
       <c r="E3">
-        <v>-1.3851</v>
+        <v>-1.3202</v>
       </c>
       <c r="F3">
-        <v>0.0649</v>
+        <v>0.1298</v>
       </c>
       <c r="G3">
         <v>0.828</v>
@@ -1646,28 +1646,28 @@
         <v>1.71</v>
       </c>
       <c r="M3">
-        <v>0.00326447</v>
+        <v>0.00652894</v>
       </c>
       <c r="N3">
-        <v>1.70673553</v>
+        <v>1.70347106</v>
       </c>
       <c r="O3">
-        <v>0.5973574355</v>
+        <v>0.5962148709999999</v>
       </c>
       <c r="P3">
-        <v>1.1093780945</v>
+        <v>1.107256189</v>
       </c>
       <c r="Q3">
-        <v>1.1993780945</v>
+        <v>1.197256189</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2269239070178095</v>
+        <v>0.2281294584842848</v>
       </c>
       <c r="T3">
-        <v>0.8899291668109383</v>
+        <v>0.8958524898541109</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>523.8216310764076</v>
+        <v>261.9108155382038</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2242207693145991</v>
+        <v>0.2234599206815668</v>
       </c>
       <c r="C4">
-        <v>6.451326127636213</v>
+        <v>6.411064538669395</v>
       </c>
       <c r="D4">
-        <v>5.753126127636214</v>
+        <v>5.777764538669395</v>
       </c>
       <c r="E4">
-        <v>-1.3202</v>
+        <v>-1.2553</v>
       </c>
       <c r="F4">
-        <v>0.1298</v>
+        <v>0.1947</v>
       </c>
       <c r="G4">
         <v>0.828</v>
@@ -1728,28 +1728,28 @@
         <v>1.71</v>
       </c>
       <c r="M4">
-        <v>0.00652894</v>
+        <v>0.009793410000000001</v>
       </c>
       <c r="N4">
-        <v>1.70347106</v>
+        <v>1.70020659</v>
       </c>
       <c r="O4">
-        <v>0.5962148709999999</v>
+        <v>0.5950723065</v>
       </c>
       <c r="P4">
-        <v>1.107256189</v>
+        <v>1.1051342835</v>
       </c>
       <c r="Q4">
-        <v>1.197256189</v>
+        <v>1.1951342835</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2281294584842848</v>
+        <v>0.2293598666820276</v>
       </c>
       <c r="T4">
-        <v>0.8958524898541109</v>
+        <v>0.9018979432693076</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>261.9108155382038</v>
+        <v>174.6072103588025</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2234599206815668</v>
+        <v>0.2226990720485344</v>
       </c>
       <c r="C5">
-        <v>6.411064538669395</v>
+        <v>6.371014890908797</v>
       </c>
       <c r="D5">
-        <v>5.777764538669395</v>
+        <v>5.802614890908797</v>
       </c>
       <c r="E5">
-        <v>-1.2553</v>
+        <v>-1.1904</v>
       </c>
       <c r="F5">
-        <v>0.1947</v>
+        <v>0.2596</v>
       </c>
       <c r="G5">
         <v>0.828</v>
@@ -1810,28 +1810,28 @@
         <v>1.71</v>
       </c>
       <c r="M5">
-        <v>0.009793410000000001</v>
+        <v>0.01305788</v>
       </c>
       <c r="N5">
-        <v>1.70020659</v>
+        <v>1.69694212</v>
       </c>
       <c r="O5">
-        <v>0.5950723065</v>
+        <v>0.5939297419999999</v>
       </c>
       <c r="P5">
-        <v>1.1051342835</v>
+        <v>1.103012378</v>
       </c>
       <c r="Q5">
-        <v>1.1951342835</v>
+        <v>1.193012378</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2293598666820276</v>
+        <v>0.23061590838389</v>
       </c>
       <c r="T5">
-        <v>0.9018979432693076</v>
+        <v>0.9080693436306544</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>174.6072103588025</v>
+        <v>130.9554077691019</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2226990720485344</v>
+        <v>0.2219382234155021</v>
       </c>
       <c r="C6">
-        <v>6.371014890908797</v>
+        <v>6.331179930865208</v>
       </c>
       <c r="D6">
-        <v>5.802614890908797</v>
+        <v>5.827679930865208</v>
       </c>
       <c r="E6">
-        <v>-1.1904</v>
+        <v>-1.1255</v>
       </c>
       <c r="F6">
-        <v>0.2596</v>
+        <v>0.3245</v>
       </c>
       <c r="G6">
         <v>0.828</v>
@@ -1892,28 +1892,28 @@
         <v>1.71</v>
       </c>
       <c r="M6">
-        <v>0.01305788</v>
+        <v>0.01632235</v>
       </c>
       <c r="N6">
-        <v>1.69694212</v>
+        <v>1.69367765</v>
       </c>
       <c r="O6">
-        <v>0.5939297419999999</v>
+        <v>0.5927871775</v>
       </c>
       <c r="P6">
-        <v>1.103012378</v>
+        <v>1.1008904725</v>
       </c>
       <c r="Q6">
-        <v>1.193012378</v>
+        <v>1.1908904725</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.23061590838389</v>
+        <v>0.2318983930689496</v>
       </c>
       <c r="T6">
-        <v>0.9080693436306544</v>
+        <v>0.9143706682101348</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>130.9554077691019</v>
+        <v>104.7643262152815</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2219382234155021</v>
+        <v>0.2211773747824698</v>
       </c>
       <c r="C7">
-        <v>6.331179930865208</v>
+        <v>6.291562452710732</v>
       </c>
       <c r="D7">
-        <v>5.827679930865208</v>
+        <v>5.852962452710732</v>
       </c>
       <c r="E7">
-        <v>-1.1255</v>
+        <v>-1.0606</v>
       </c>
       <c r="F7">
-        <v>0.3245</v>
+        <v>0.3894</v>
       </c>
       <c r="G7">
         <v>0.828</v>
@@ -1974,28 +1974,28 @@
         <v>1.71</v>
       </c>
       <c r="M7">
-        <v>0.01632235</v>
+        <v>0.01958682</v>
       </c>
       <c r="N7">
-        <v>1.69367765</v>
+        <v>1.69041318</v>
       </c>
       <c r="O7">
-        <v>0.5927871775</v>
+        <v>0.5916446129999999</v>
       </c>
       <c r="P7">
-        <v>1.1008904725</v>
+        <v>1.098768567</v>
       </c>
       <c r="Q7">
-        <v>1.1908904725</v>
+        <v>1.188768567</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2318983930689496</v>
+        <v>0.2332081646622019</v>
       </c>
       <c r="T7">
-        <v>0.9143706682101348</v>
+        <v>0.9208060635253488</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>104.7643262152815</v>
+        <v>87.30360517940125</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2211773747824698</v>
+        <v>0.2204165261494375</v>
       </c>
       <c r="C8">
-        <v>6.291562452710732</v>
+        <v>6.25216529931715</v>
       </c>
       <c r="D8">
-        <v>5.852962452710732</v>
+        <v>5.87846529931715</v>
       </c>
       <c r="E8">
-        <v>-1.0606</v>
+        <v>-0.9957</v>
       </c>
       <c r="F8">
-        <v>0.3894</v>
+        <v>0.4543</v>
       </c>
       <c r="G8">
         <v>0.828</v>
@@ -2056,28 +2056,28 @@
         <v>1.71</v>
       </c>
       <c r="M8">
-        <v>0.01958682</v>
+        <v>0.02285129</v>
       </c>
       <c r="N8">
-        <v>1.69041318</v>
+        <v>1.68714871</v>
       </c>
       <c r="O8">
-        <v>0.5916446129999999</v>
+        <v>0.5905020485</v>
       </c>
       <c r="P8">
-        <v>1.098768567</v>
+        <v>1.0966466615</v>
       </c>
       <c r="Q8">
-        <v>1.188768567</v>
+        <v>1.1866466615</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2332081646622019</v>
+        <v>0.2345461033864919</v>
       </c>
       <c r="T8">
-        <v>0.9208060635253488</v>
+        <v>0.9273798544387393</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>87.30360517940125</v>
+        <v>74.83166158234394</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2204165261494374</v>
+        <v>0.2196556775164051</v>
       </c>
       <c r="C9">
-        <v>6.252165299317151</v>
+        <v>6.212991363321539</v>
       </c>
       <c r="D9">
-        <v>5.878465299317151</v>
+        <v>5.904191363321538</v>
       </c>
       <c r="E9">
-        <v>-0.9956999999999999</v>
+        <v>-0.9308</v>
       </c>
       <c r="F9">
-        <v>0.4543</v>
+        <v>0.5192</v>
       </c>
       <c r="G9">
         <v>0.828</v>
@@ -2138,28 +2138,28 @@
         <v>1.71</v>
       </c>
       <c r="M9">
-        <v>0.02285129</v>
+        <v>0.02611576</v>
       </c>
       <c r="N9">
-        <v>1.68714871</v>
+        <v>1.68388424</v>
       </c>
       <c r="O9">
-        <v>0.5905020485</v>
+        <v>0.5893594839999999</v>
       </c>
       <c r="P9">
-        <v>1.0966466615</v>
+        <v>1.094524756</v>
       </c>
       <c r="Q9">
-        <v>1.1866466615</v>
+        <v>1.184524756</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2345461033864919</v>
+        <v>0.235913127735223</v>
       </c>
       <c r="T9">
-        <v>0.9273798544387393</v>
+        <v>0.9340965538502471</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>74.83166158234393</v>
+        <v>65.47770388455095</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2196556775164051</v>
+        <v>0.2188948288833728</v>
       </c>
       <c r="C10">
-        <v>6.212991363321539</v>
+        <v>6.174043588220015</v>
       </c>
       <c r="D10">
-        <v>5.904191363321538</v>
+        <v>5.930143588220015</v>
       </c>
       <c r="E10">
-        <v>-0.9308</v>
+        <v>-0.8659</v>
       </c>
       <c r="F10">
-        <v>0.5192</v>
+        <v>0.5841</v>
       </c>
       <c r="G10">
         <v>0.828</v>
@@ -2220,28 +2220,28 @@
         <v>1.71</v>
       </c>
       <c r="M10">
-        <v>0.02611576</v>
+        <v>0.02938023</v>
       </c>
       <c r="N10">
-        <v>1.68388424</v>
+        <v>1.68061977</v>
       </c>
       <c r="O10">
-        <v>0.5893594839999999</v>
+        <v>0.5882169195</v>
       </c>
       <c r="P10">
-        <v>1.094524756</v>
+        <v>1.0924028505</v>
       </c>
       <c r="Q10">
-        <v>1.184524756</v>
+        <v>1.1824028505</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.235913127735223</v>
+        <v>0.237310196575135</v>
       </c>
       <c r="T10">
-        <v>0.9340965538502471</v>
+        <v>0.9409608730290409</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>65.47770388455095</v>
+        <v>58.20240345293418</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2188948288833728</v>
+        <v>0.2181339802503405</v>
       </c>
       <c r="C11">
-        <v>6.174043588220015</v>
+        <v>6.13532496949043</v>
       </c>
       <c r="D11">
-        <v>5.930143588220015</v>
+        <v>5.95632496949043</v>
       </c>
       <c r="E11">
-        <v>-0.8659</v>
+        <v>-0.8009999999999999</v>
       </c>
       <c r="F11">
-        <v>0.5841</v>
+        <v>0.649</v>
       </c>
       <c r="G11">
         <v>0.828</v>
@@ -2302,28 +2302,28 @@
         <v>1.71</v>
       </c>
       <c r="M11">
-        <v>0.02938023</v>
+        <v>0.0326447</v>
       </c>
       <c r="N11">
-        <v>1.68061977</v>
+        <v>1.6773553</v>
       </c>
       <c r="O11">
-        <v>0.5882169195</v>
+        <v>0.5870743549999999</v>
       </c>
       <c r="P11">
-        <v>1.0924028505</v>
+        <v>1.090280945</v>
       </c>
       <c r="Q11">
-        <v>1.1824028505</v>
+        <v>1.180280945</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.237310196575135</v>
+        <v>0.2387383113892672</v>
       </c>
       <c r="T11">
-        <v>0.9409608730290409</v>
+        <v>0.94797773263403</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>58.20240345293418</v>
+        <v>52.38216310764075</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2181339802503405</v>
+        <v>0.2173731316173082</v>
       </c>
       <c r="C12">
-        <v>6.13532496949043</v>
+        <v>6.096838555744958</v>
       </c>
       <c r="D12">
-        <v>5.95632496949043</v>
+        <v>5.982738555744957</v>
       </c>
       <c r="E12">
-        <v>-0.8009999999999999</v>
+        <v>-0.7361</v>
       </c>
       <c r="F12">
-        <v>0.649</v>
+        <v>0.7139</v>
       </c>
       <c r="G12">
         <v>0.828</v>
@@ -2384,28 +2384,28 @@
         <v>1.71</v>
       </c>
       <c r="M12">
-        <v>0.0326447</v>
+        <v>0.03590917</v>
       </c>
       <c r="N12">
-        <v>1.6773553</v>
+        <v>1.67409083</v>
       </c>
       <c r="O12">
-        <v>0.5870743549999999</v>
+        <v>0.5859317904999999</v>
       </c>
       <c r="P12">
-        <v>1.090280945</v>
+        <v>1.0881590395</v>
       </c>
       <c r="Q12">
-        <v>1.180280945</v>
+        <v>1.1781590395</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2387383113892672</v>
+        <v>0.2401985186711328</v>
       </c>
       <c r="T12">
-        <v>0.94797773263403</v>
+        <v>0.9551522744773335</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>52.38216310764075</v>
+        <v>47.62014827967341</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2173731316173082</v>
+        <v>0.2166122829842758</v>
       </c>
       <c r="C13">
-        <v>6.096838555744958</v>
+        <v>6.058587449913461</v>
       </c>
       <c r="D13">
-        <v>5.982738555744957</v>
+        <v>6.009387449913461</v>
       </c>
       <c r="E13">
-        <v>-0.7361</v>
+        <v>-0.6711999999999999</v>
       </c>
       <c r="F13">
-        <v>0.7139</v>
+        <v>0.7788</v>
       </c>
       <c r="G13">
         <v>0.828</v>
@@ -2466,28 +2466,28 @@
         <v>1.71</v>
       </c>
       <c r="M13">
-        <v>0.03590917</v>
+        <v>0.03917364</v>
       </c>
       <c r="N13">
-        <v>1.67409083</v>
+        <v>1.67082636</v>
       </c>
       <c r="O13">
-        <v>0.5859317904999999</v>
+        <v>0.5847892259999999</v>
       </c>
       <c r="P13">
-        <v>1.0881590395</v>
+        <v>1.086037134</v>
       </c>
       <c r="Q13">
-        <v>1.1781590395</v>
+        <v>1.176037134</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2401985186711328</v>
+        <v>0.2416919124821316</v>
       </c>
       <c r="T13">
-        <v>0.9551522744773335</v>
+        <v>0.9624898740898029</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>47.62014827967341</v>
+        <v>43.65180258970062</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2166122829842758</v>
+        <v>0.2158514343512435</v>
       </c>
       <c r="C14">
-        <v>6.058587449913461</v>
+        <v>6.02057481045865</v>
       </c>
       <c r="D14">
-        <v>6.009387449913461</v>
+        <v>6.03627481045865</v>
       </c>
       <c r="E14">
-        <v>-0.6711999999999999</v>
+        <v>-0.6063</v>
       </c>
       <c r="F14">
-        <v>0.7788</v>
+        <v>0.8437</v>
       </c>
       <c r="G14">
         <v>0.828</v>
@@ -2548,28 +2548,28 @@
         <v>1.71</v>
       </c>
       <c r="M14">
-        <v>0.03917364</v>
+        <v>0.04243811</v>
       </c>
       <c r="N14">
-        <v>1.67082636</v>
+        <v>1.66756189</v>
       </c>
       <c r="O14">
-        <v>0.5847892259999999</v>
+        <v>0.5836466615</v>
       </c>
       <c r="P14">
-        <v>1.086037134</v>
+        <v>1.0839152285</v>
       </c>
       <c r="Q14">
-        <v>1.176037134</v>
+        <v>1.1739152285</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2416919124821316</v>
+        <v>0.2432196371853374</v>
       </c>
       <c r="T14">
-        <v>0.9624898740898029</v>
+        <v>0.9699961541531338</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>43.65180258970062</v>
+        <v>40.29397162126212</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2158514343512435</v>
+        <v>0.2150905857182112</v>
       </c>
       <c r="C15">
-        <v>6.02057481045865</v>
+        <v>5.982803852623992</v>
       </c>
       <c r="D15">
-        <v>6.03627481045865</v>
+        <v>6.063403852623991</v>
       </c>
       <c r="E15">
-        <v>-0.6063</v>
+        <v>-0.5413999999999999</v>
       </c>
       <c r="F15">
-        <v>0.8437</v>
+        <v>0.9086000000000001</v>
       </c>
       <c r="G15">
         <v>0.828</v>
@@ -2630,28 +2630,28 @@
         <v>1.71</v>
       </c>
       <c r="M15">
-        <v>0.04243811</v>
+        <v>0.04570258</v>
       </c>
       <c r="N15">
-        <v>1.66756189</v>
+        <v>1.66429742</v>
       </c>
       <c r="O15">
-        <v>0.5836466615</v>
+        <v>0.5825040969999999</v>
       </c>
       <c r="P15">
-        <v>1.0839152285</v>
+        <v>1.081793323</v>
       </c>
       <c r="Q15">
-        <v>1.1739152285</v>
+        <v>1.171793323</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2432196371853374</v>
+        <v>0.2447828903700131</v>
       </c>
       <c r="T15">
-        <v>0.9699961541531338</v>
+        <v>0.9776769988691003</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>40.29397162126212</v>
+        <v>37.41583079117196</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2150905857182112</v>
+        <v>0.2143297370851789</v>
       </c>
       <c r="C16">
-        <v>5.982803852623992</v>
+        <v>5.945277849715437</v>
       </c>
       <c r="D16">
-        <v>6.063403852623991</v>
+        <v>6.090777849715437</v>
       </c>
       <c r="E16">
-        <v>-0.5413999999999999</v>
+        <v>-0.4764999999999998</v>
       </c>
       <c r="F16">
-        <v>0.9086000000000001</v>
+        <v>0.9735000000000001</v>
       </c>
       <c r="G16">
         <v>0.828</v>
@@ -2712,28 +2712,28 @@
         <v>1.71</v>
       </c>
       <c r="M16">
-        <v>0.04570258</v>
+        <v>0.04896705000000001</v>
       </c>
       <c r="N16">
-        <v>1.66429742</v>
+        <v>1.66103295</v>
       </c>
       <c r="O16">
-        <v>0.5825040969999999</v>
+        <v>0.5813615325</v>
       </c>
       <c r="P16">
-        <v>1.081793323</v>
+        <v>1.0796714175</v>
       </c>
       <c r="Q16">
-        <v>1.171793323</v>
+        <v>1.1696714175</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2447828903700131</v>
+        <v>0.2463829259825634</v>
       </c>
       <c r="T16">
-        <v>0.9776769988691003</v>
+        <v>0.9855385693430895</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>37.41583079117196</v>
+        <v>34.9214420717605</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2143297370851789</v>
+        <v>0.2135688884521466</v>
       </c>
       <c r="C17">
-        <v>5.945277849715437</v>
+        <v>5.908000134418011</v>
       </c>
       <c r="D17">
-        <v>6.090777849715437</v>
+        <v>6.118400134418011</v>
       </c>
       <c r="E17">
-        <v>-0.4764999999999999</v>
+        <v>-0.4116</v>
       </c>
       <c r="F17">
-        <v>0.9735</v>
+        <v>1.0384</v>
       </c>
       <c r="G17">
         <v>0.828</v>
@@ -2794,28 +2794,28 @@
         <v>1.71</v>
       </c>
       <c r="M17">
-        <v>0.04896705</v>
+        <v>0.05223152</v>
       </c>
       <c r="N17">
-        <v>1.66103295</v>
+        <v>1.65776848</v>
       </c>
       <c r="O17">
-        <v>0.5813615325</v>
+        <v>0.5802189679999999</v>
       </c>
       <c r="P17">
-        <v>1.0796714175</v>
+        <v>1.077549512</v>
       </c>
       <c r="Q17">
-        <v>1.1696714175</v>
+        <v>1.167549512</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2463829259825634</v>
+        <v>0.2480210576811269</v>
       </c>
       <c r="T17">
-        <v>0.9855385693430895</v>
+        <v>0.9935873200664593</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>34.9214420717605</v>
+        <v>32.73885194227547</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2135688884521466</v>
+        <v>0.2128080398191143</v>
       </c>
       <c r="C18">
-        <v>5.908000134418011</v>
+        <v>5.870974100148396</v>
       </c>
       <c r="D18">
-        <v>6.118400134418011</v>
+        <v>6.146274100148395</v>
       </c>
       <c r="E18">
-        <v>-0.4116</v>
+        <v>-0.3466999999999998</v>
       </c>
       <c r="F18">
-        <v>1.0384</v>
+        <v>1.1033</v>
       </c>
       <c r="G18">
         <v>0.828</v>
@@ -2876,28 +2876,28 @@
         <v>1.71</v>
       </c>
       <c r="M18">
-        <v>0.05223152</v>
+        <v>0.05549599000000001</v>
       </c>
       <c r="N18">
-        <v>1.65776848</v>
+        <v>1.65450401</v>
       </c>
       <c r="O18">
-        <v>0.5802189679999999</v>
+        <v>0.5790764034999999</v>
       </c>
       <c r="P18">
-        <v>1.077549512</v>
+        <v>1.0754276065</v>
       </c>
       <c r="Q18">
-        <v>1.167549512</v>
+        <v>1.1654276065</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2480210576811269</v>
+        <v>0.2496986624326678</v>
       </c>
       <c r="T18">
-        <v>0.9935873200664593</v>
+        <v>1.001830016590392</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>32.73885194227547</v>
+        <v>30.81303712214161</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2128080398191143</v>
+        <v>0.2120471911860819</v>
       </c>
       <c r="C19">
-        <v>5.870974100148396</v>
+        <v>5.834203202444662</v>
       </c>
       <c r="D19">
-        <v>6.146274100148395</v>
+        <v>6.174403202444662</v>
       </c>
       <c r="E19">
-        <v>-0.3466999999999998</v>
+        <v>-0.2817999999999998</v>
       </c>
       <c r="F19">
-        <v>1.1033</v>
+        <v>1.1682</v>
       </c>
       <c r="G19">
         <v>0.828</v>
@@ -2958,28 +2958,28 @@
         <v>1.71</v>
       </c>
       <c r="M19">
-        <v>0.05549599000000001</v>
+        <v>0.05876046</v>
       </c>
       <c r="N19">
-        <v>1.65450401</v>
+        <v>1.65123954</v>
       </c>
       <c r="O19">
-        <v>0.5790764034999999</v>
+        <v>0.5779338389999999</v>
       </c>
       <c r="P19">
-        <v>1.0754276065</v>
+        <v>1.073305701</v>
       </c>
       <c r="Q19">
-        <v>1.1654276065</v>
+        <v>1.163305701</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2496986624326678</v>
+        <v>0.2514171843732706</v>
       </c>
       <c r="T19">
-        <v>1.001830016590392</v>
+        <v>1.010273754492958</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>30.81303712214161</v>
+        <v>29.10120172646708</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2120471911860819</v>
+        <v>0.2112863425530496</v>
       </c>
       <c r="C20">
-        <v>5.834203202444662</v>
+        <v>5.797690960394321</v>
       </c>
       <c r="D20">
-        <v>6.174403202444661</v>
+        <v>6.202790960394321</v>
       </c>
       <c r="E20">
-        <v>-0.2818000000000001</v>
+        <v>-0.2168999999999999</v>
       </c>
       <c r="F20">
-        <v>1.1682</v>
+        <v>1.2331</v>
       </c>
       <c r="G20">
         <v>0.828</v>
@@ -3040,28 +3040,28 @@
         <v>1.71</v>
       </c>
       <c r="M20">
-        <v>0.05876045999999999</v>
+        <v>0.06202493</v>
       </c>
       <c r="N20">
-        <v>1.65123954</v>
+        <v>1.64797507</v>
       </c>
       <c r="O20">
-        <v>0.5779338389999999</v>
+        <v>0.5767912745</v>
       </c>
       <c r="P20">
-        <v>1.073305701</v>
+        <v>1.0711837955</v>
       </c>
       <c r="Q20">
-        <v>1.163305701</v>
+        <v>1.1611837955</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2514171843732706</v>
+        <v>0.2531781389543822</v>
       </c>
       <c r="T20">
-        <v>1.010273754492958</v>
+        <v>1.018925979751142</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>29.10120172646709</v>
+        <v>27.56955953033724</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2112863425530496</v>
+        <v>0.2105254939200172</v>
       </c>
       <c r="C21">
-        <v>5.797690960394321</v>
+        <v>5.761440958101979</v>
       </c>
       <c r="D21">
-        <v>6.202790960394321</v>
+        <v>6.231440958101978</v>
       </c>
       <c r="E21">
-        <v>-0.2168999999999999</v>
+        <v>-0.1519999999999999</v>
       </c>
       <c r="F21">
-        <v>1.2331</v>
+        <v>1.298</v>
       </c>
       <c r="G21">
         <v>0.828</v>
@@ -3122,28 +3122,28 @@
         <v>1.71</v>
       </c>
       <c r="M21">
-        <v>0.06202493</v>
+        <v>0.0652894</v>
       </c>
       <c r="N21">
-        <v>1.64797507</v>
+        <v>1.6447106</v>
       </c>
       <c r="O21">
-        <v>0.5767912745</v>
+        <v>0.57564871</v>
       </c>
       <c r="P21">
-        <v>1.0711837955</v>
+        <v>1.06906189</v>
       </c>
       <c r="Q21">
-        <v>1.1611837955</v>
+        <v>1.15906189</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2531781389543822</v>
+        <v>0.2549831174000216</v>
       </c>
       <c r="T21">
-        <v>1.018925979751142</v>
+        <v>1.027794510640781</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>27.56955953033724</v>
+        <v>26.19108155382037</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2105254939200172</v>
+        <v>0.2097646452869849</v>
       </c>
       <c r="C22">
-        <v>5.761440958101979</v>
+        <v>5.725456846197824</v>
       </c>
       <c r="D22">
-        <v>6.231440958101978</v>
+        <v>6.260356846197824</v>
       </c>
       <c r="E22">
-        <v>-0.1519999999999999</v>
+        <v>-0.08709999999999973</v>
       </c>
       <c r="F22">
-        <v>1.298</v>
+        <v>1.3629</v>
       </c>
       <c r="G22">
         <v>0.828</v>
@@ -3204,28 +3204,28 @@
         <v>1.71</v>
       </c>
       <c r="M22">
-        <v>0.0652894</v>
+        <v>0.06855387</v>
       </c>
       <c r="N22">
-        <v>1.6447106</v>
+        <v>1.64144613</v>
       </c>
       <c r="O22">
-        <v>0.57564871</v>
+        <v>0.5745061455</v>
       </c>
       <c r="P22">
-        <v>1.06906189</v>
+        <v>1.0669399845</v>
       </c>
       <c r="Q22">
-        <v>1.15906189</v>
+        <v>1.1569399845</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2549831174000216</v>
+        <v>0.2568337915025126</v>
       </c>
       <c r="T22">
-        <v>1.027794510640781</v>
+        <v>1.036887561299778</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>26.19108155382037</v>
+        <v>24.94388719411464</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2097646452869849</v>
+        <v>0.2090037966539526</v>
       </c>
       <c r="C23">
-        <v>5.725456846197824</v>
+        <v>5.689742343388332</v>
       </c>
       <c r="D23">
-        <v>6.260356846197824</v>
+        <v>6.289542343388331</v>
       </c>
       <c r="E23">
-        <v>-0.08709999999999996</v>
+        <v>-0.0222</v>
       </c>
       <c r="F23">
-        <v>1.3629</v>
+        <v>1.4278</v>
       </c>
       <c r="G23">
         <v>0.828</v>
@@ -3286,28 +3286,28 @@
         <v>1.71</v>
       </c>
       <c r="M23">
-        <v>0.06855387</v>
+        <v>0.07181833999999999</v>
       </c>
       <c r="N23">
-        <v>1.64144613</v>
+        <v>1.63818166</v>
       </c>
       <c r="O23">
-        <v>0.5745061455</v>
+        <v>0.573363581</v>
       </c>
       <c r="P23">
-        <v>1.0669399845</v>
+        <v>1.064818079</v>
       </c>
       <c r="Q23">
-        <v>1.1569399845</v>
+        <v>1.154818079</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2568337915025126</v>
+        <v>0.2587319187871187</v>
       </c>
       <c r="T23">
-        <v>1.036887561299778</v>
+        <v>1.046213767103878</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>24.94388719411464</v>
+        <v>23.8100741398367</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2090037966539526</v>
+        <v>0.2082429480209203</v>
       </c>
       <c r="C24">
-        <v>5.689742343388332</v>
+        <v>5.654301238050534</v>
       </c>
       <c r="D24">
-        <v>6.289542343388331</v>
+        <v>6.319001238050534</v>
       </c>
       <c r="E24">
-        <v>-0.0222</v>
+        <v>0.04270000000000018</v>
       </c>
       <c r="F24">
-        <v>1.4278</v>
+        <v>1.4927</v>
       </c>
       <c r="G24">
         <v>0.828</v>
@@ -3368,28 +3368,28 @@
         <v>1.71</v>
       </c>
       <c r="M24">
-        <v>0.07181833999999999</v>
+        <v>0.07508281</v>
       </c>
       <c r="N24">
-        <v>1.63818166</v>
+        <v>1.63491719</v>
       </c>
       <c r="O24">
-        <v>0.573363581</v>
+        <v>0.5722210164999999</v>
       </c>
       <c r="P24">
-        <v>1.064818079</v>
+        <v>1.0626961735</v>
       </c>
       <c r="Q24">
-        <v>1.154818079</v>
+        <v>1.1526961735</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2587319187871187</v>
+        <v>0.2606793480791172</v>
       </c>
       <c r="T24">
-        <v>1.046213767103878</v>
+        <v>1.055782212019772</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>23.8100741398367</v>
+        <v>22.77485352506119</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2082429480209203</v>
+        <v>0.207482099387888</v>
       </c>
       <c r="C25">
-        <v>5.654301238050534</v>
+        <v>5.619137389871312</v>
       </c>
       <c r="D25">
-        <v>6.319001238050534</v>
+        <v>6.348737389871311</v>
       </c>
       <c r="E25">
-        <v>0.04270000000000018</v>
+        <v>0.1076000000000001</v>
       </c>
       <c r="F25">
-        <v>1.4927</v>
+        <v>1.5576</v>
       </c>
       <c r="G25">
         <v>0.828</v>
@@ -3450,28 +3450,28 @@
         <v>1.71</v>
       </c>
       <c r="M25">
-        <v>0.07508281</v>
+        <v>0.07834728000000001</v>
       </c>
       <c r="N25">
-        <v>1.63491719</v>
+        <v>1.63165272</v>
       </c>
       <c r="O25">
-        <v>0.5722210164999999</v>
+        <v>0.571078452</v>
       </c>
       <c r="P25">
-        <v>1.0626961735</v>
+        <v>1.060574268</v>
       </c>
       <c r="Q25">
-        <v>1.1526961735</v>
+        <v>1.150574268</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2606793480791172</v>
+        <v>0.2626780255103789</v>
       </c>
       <c r="T25">
-        <v>1.055782212019772</v>
+        <v>1.065602458117663</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>22.77485352506119</v>
+        <v>21.82590129485031</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.207482099387888</v>
+        <v>0.2067212507548557</v>
       </c>
       <c r="C26">
-        <v>5.619137389871312</v>
+        <v>5.584254731533186</v>
       </c>
       <c r="D26">
-        <v>6.348737389871311</v>
+        <v>6.378754731533185</v>
       </c>
       <c r="E26">
-        <v>0.1076000000000001</v>
+        <v>0.1725000000000001</v>
       </c>
       <c r="F26">
-        <v>1.5576</v>
+        <v>1.6225</v>
       </c>
       <c r="G26">
         <v>0.828</v>
@@ -3532,28 +3532,28 @@
         <v>1.71</v>
       </c>
       <c r="M26">
-        <v>0.07834728000000001</v>
+        <v>0.08161175</v>
       </c>
       <c r="N26">
-        <v>1.63165272</v>
+        <v>1.62838825</v>
       </c>
       <c r="O26">
-        <v>0.571078452</v>
+        <v>0.5699358874999999</v>
       </c>
       <c r="P26">
-        <v>1.060574268</v>
+        <v>1.0584523625</v>
       </c>
       <c r="Q26">
-        <v>1.150574268</v>
+        <v>1.1484523625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2626780255103789</v>
+        <v>0.2647300010064742</v>
       </c>
       <c r="T26">
-        <v>1.065602458117663</v>
+        <v>1.075684577444832</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>21.82590129485031</v>
+        <v>20.9528652430563</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2067212507548557</v>
+        <v>0.2059604021218233</v>
       </c>
       <c r="C27">
-        <v>5.584254731533186</v>
+        <v>5.549657270448168</v>
       </c>
       <c r="D27">
-        <v>6.378754731533185</v>
+        <v>6.409057270448168</v>
       </c>
       <c r="E27">
-        <v>0.1725000000000001</v>
+        <v>0.2374000000000001</v>
       </c>
       <c r="F27">
-        <v>1.6225</v>
+        <v>1.6874</v>
       </c>
       <c r="G27">
         <v>0.828</v>
@@ -3614,28 +3614,28 @@
         <v>1.71</v>
       </c>
       <c r="M27">
-        <v>0.08161175</v>
+        <v>0.08487622</v>
       </c>
       <c r="N27">
-        <v>1.62838825</v>
+        <v>1.62512378</v>
       </c>
       <c r="O27">
-        <v>0.5699358874999999</v>
+        <v>0.568793323</v>
       </c>
       <c r="P27">
-        <v>1.0584523625</v>
+        <v>1.056330457</v>
       </c>
       <c r="Q27">
-        <v>1.1484523625</v>
+        <v>1.146330457</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2647300010064742</v>
+        <v>0.2668374352997612</v>
       </c>
       <c r="T27">
-        <v>1.075684577444832</v>
+        <v>1.086039186483546</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>20.9528652430563</v>
+        <v>20.14698581063106</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2059604021218233</v>
+        <v>0.205199553488791</v>
       </c>
       <c r="C28">
-        <v>5.549657270448168</v>
+        <v>5.515349090541247</v>
       </c>
       <c r="D28">
-        <v>6.409057270448168</v>
+        <v>6.439649090541247</v>
       </c>
       <c r="E28">
-        <v>0.2374000000000001</v>
+        <v>0.3023000000000002</v>
       </c>
       <c r="F28">
-        <v>1.6874</v>
+        <v>1.7523</v>
       </c>
       <c r="G28">
         <v>0.828</v>
@@ -3696,28 +3696,28 @@
         <v>1.71</v>
       </c>
       <c r="M28">
-        <v>0.08487622</v>
+        <v>0.08814069000000001</v>
       </c>
       <c r="N28">
-        <v>1.62512378</v>
+        <v>1.62185931</v>
       </c>
       <c r="O28">
-        <v>0.568793323</v>
+        <v>0.5676507585</v>
       </c>
       <c r="P28">
-        <v>1.056330457</v>
+        <v>1.0542085515</v>
       </c>
       <c r="Q28">
-        <v>1.146330457</v>
+        <v>1.1442085515</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2668374352997612</v>
+        <v>0.2690026075188918</v>
       </c>
       <c r="T28">
-        <v>1.086039186483546</v>
+        <v>1.096677483441128</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>20.14698581063106</v>
+        <v>19.40080115097805</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.205199553488791</v>
+        <v>0.2044387048557587</v>
       </c>
       <c r="C29">
-        <v>5.515349090541247</v>
+        <v>5.481334354085231</v>
       </c>
       <c r="D29">
-        <v>6.439649090541247</v>
+        <v>6.47053435408523</v>
       </c>
       <c r="E29">
-        <v>0.3023000000000002</v>
+        <v>0.3672000000000002</v>
       </c>
       <c r="F29">
-        <v>1.7523</v>
+        <v>1.8172</v>
       </c>
       <c r="G29">
         <v>0.828</v>
@@ -3778,28 +3778,28 @@
         <v>1.71</v>
       </c>
       <c r="M29">
-        <v>0.08814069000000001</v>
+        <v>0.09140516</v>
       </c>
       <c r="N29">
-        <v>1.62185931</v>
+        <v>1.61859484</v>
       </c>
       <c r="O29">
-        <v>0.5676507585</v>
+        <v>0.566508194</v>
       </c>
       <c r="P29">
-        <v>1.0542085515</v>
+        <v>1.052086646</v>
       </c>
       <c r="Q29">
-        <v>1.1442085515</v>
+        <v>1.142086646</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2690026075188918</v>
+        <v>0.2712279234107759</v>
       </c>
       <c r="T29">
-        <v>1.096677483441128</v>
+        <v>1.107611288647532</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>19.40080115097805</v>
+        <v>18.70791539558598</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2044387048557587</v>
+        <v>0.2036778562227263</v>
       </c>
       <c r="C30">
-        <v>5.481334354085231</v>
+        <v>5.447617303588606</v>
       </c>
       <c r="D30">
-        <v>6.47053435408523</v>
+        <v>6.501717303588606</v>
       </c>
       <c r="E30">
-        <v>0.3672000000000002</v>
+        <v>0.4321000000000004</v>
       </c>
       <c r="F30">
-        <v>1.8172</v>
+        <v>1.8821</v>
       </c>
       <c r="G30">
         <v>0.828</v>
@@ -3860,28 +3860,28 @@
         <v>1.71</v>
       </c>
       <c r="M30">
-        <v>0.09140516</v>
+        <v>0.09466963000000002</v>
       </c>
       <c r="N30">
-        <v>1.61859484</v>
+        <v>1.61533037</v>
       </c>
       <c r="O30">
-        <v>0.566508194</v>
+        <v>0.5653656294999999</v>
       </c>
       <c r="P30">
-        <v>1.052086646</v>
+        <v>1.0499647405</v>
       </c>
       <c r="Q30">
-        <v>1.142086646</v>
+        <v>1.1399647405</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2712279234107759</v>
+        <v>0.273515924257361</v>
       </c>
       <c r="T30">
-        <v>1.107611288647532</v>
+        <v>1.118853088366793</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>18.70791539558598</v>
+        <v>18.0628148647037</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2036778562227263</v>
+        <v>0.202917007589694</v>
       </c>
       <c r="C31">
-        <v>5.447617303588606</v>
+        <v>5.414202263738283</v>
       </c>
       <c r="D31">
-        <v>6.501717303588606</v>
+        <v>6.533202263738283</v>
       </c>
       <c r="E31">
-        <v>0.4320999999999999</v>
+        <v>0.4970000000000001</v>
       </c>
       <c r="F31">
-        <v>1.8821</v>
+        <v>1.947</v>
       </c>
       <c r="G31">
         <v>0.828</v>
@@ -3942,28 +3942,28 @@
         <v>1.71</v>
       </c>
       <c r="M31">
-        <v>0.09466962999999999</v>
+        <v>0.0979341</v>
       </c>
       <c r="N31">
-        <v>1.61533037</v>
+        <v>1.6120659</v>
       </c>
       <c r="O31">
-        <v>0.5653656294999999</v>
+        <v>0.564223065</v>
       </c>
       <c r="P31">
-        <v>1.0499647405</v>
+        <v>1.047842835</v>
       </c>
       <c r="Q31">
-        <v>1.1399647405</v>
+        <v>1.137842835</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.273515924257361</v>
+        <v>0.2758692965567057</v>
       </c>
       <c r="T31">
-        <v>1.118853088366793</v>
+        <v>1.130416082363747</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>18.06281486470371</v>
+        <v>17.46072103588025</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.202917007589694</v>
+        <v>0.2021561589566617</v>
       </c>
       <c r="C32">
-        <v>5.414202263738283</v>
+        <v>5.381093643399041</v>
       </c>
       <c r="D32">
-        <v>6.533202263738283</v>
+        <v>6.564993643399041</v>
       </c>
       <c r="E32">
-        <v>0.4970000000000001</v>
+        <v>0.5619000000000003</v>
       </c>
       <c r="F32">
-        <v>1.947</v>
+        <v>2.0119</v>
       </c>
       <c r="G32">
         <v>0.828</v>
@@ -4024,28 +4024,28 @@
         <v>1.71</v>
       </c>
       <c r="M32">
-        <v>0.0979341</v>
+        <v>0.10119857</v>
       </c>
       <c r="N32">
-        <v>1.6120659</v>
+        <v>1.60880143</v>
       </c>
       <c r="O32">
-        <v>0.564223065</v>
+        <v>0.5630805004999999</v>
       </c>
       <c r="P32">
-        <v>1.047842835</v>
+        <v>1.0457209295</v>
       </c>
       <c r="Q32">
-        <v>1.137842835</v>
+        <v>1.1357209295</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2758692965567057</v>
+        <v>0.2782908825458865</v>
       </c>
       <c r="T32">
-        <v>1.130416082363747</v>
+        <v>1.14231423560699</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>17.46072103588025</v>
+        <v>16.89747197020669</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2021561589566617</v>
+        <v>0.2013953103236294</v>
       </c>
       <c r="C33">
-        <v>5.381093643399041</v>
+        <v>5.348295937671642</v>
       </c>
       <c r="D33">
-        <v>6.564993643399041</v>
+        <v>6.597095937671642</v>
       </c>
       <c r="E33">
-        <v>0.5619000000000003</v>
+        <v>0.6268</v>
       </c>
       <c r="F33">
-        <v>2.0119</v>
+        <v>2.0768</v>
       </c>
       <c r="G33">
         <v>0.828</v>
@@ -4106,28 +4106,28 @@
         <v>1.71</v>
       </c>
       <c r="M33">
-        <v>0.10119857</v>
+        <v>0.10446304</v>
       </c>
       <c r="N33">
-        <v>1.60880143</v>
+        <v>1.60553696</v>
       </c>
       <c r="O33">
-        <v>0.5630805004999999</v>
+        <v>0.561937936</v>
       </c>
       <c r="P33">
-        <v>1.0457209295</v>
+        <v>1.043599024</v>
       </c>
       <c r="Q33">
-        <v>1.1357209295</v>
+        <v>1.133599024</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2782908825458865</v>
+        <v>0.2807836916523961</v>
       </c>
       <c r="T33">
-        <v>1.14231423560699</v>
+        <v>1.154562334533857</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.89747197020669</v>
+        <v>16.36942597113774</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2013953103236294</v>
+        <v>0.200634461690597</v>
       </c>
       <c r="C34">
-        <v>5.348295937671642</v>
+        <v>5.315813730011636</v>
       </c>
       <c r="D34">
-        <v>6.597095937671642</v>
+        <v>6.629513730011636</v>
       </c>
       <c r="E34">
-        <v>0.6268</v>
+        <v>0.6917000000000002</v>
       </c>
       <c r="F34">
-        <v>2.0768</v>
+        <v>2.1417</v>
       </c>
       <c r="G34">
         <v>0.828</v>
@@ -4188,28 +4188,28 @@
         <v>1.71</v>
       </c>
       <c r="M34">
-        <v>0.10446304</v>
+        <v>0.10772751</v>
       </c>
       <c r="N34">
-        <v>1.60553696</v>
+        <v>1.60227249</v>
       </c>
       <c r="O34">
-        <v>0.561937936</v>
+        <v>0.5607953715</v>
       </c>
       <c r="P34">
-        <v>1.043599024</v>
+        <v>1.0414771185</v>
       </c>
       <c r="Q34">
-        <v>1.133599024</v>
+        <v>1.1314771185</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2807836916523961</v>
+        <v>0.2833509129710404</v>
       </c>
       <c r="T34">
-        <v>1.154562334533857</v>
+        <v>1.167176048354063</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>16.36942597113774</v>
+        <v>15.87338275989114</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.200634461690597</v>
+        <v>0.1998736130575647</v>
       </c>
       <c r="C35">
-        <v>5.315813730011636</v>
+        <v>5.283651694410924</v>
       </c>
       <c r="D35">
-        <v>6.629513730011636</v>
+        <v>6.662251694410925</v>
       </c>
       <c r="E35">
-        <v>0.6917000000000002</v>
+        <v>0.7566000000000004</v>
       </c>
       <c r="F35">
-        <v>2.1417</v>
+        <v>2.2066</v>
       </c>
       <c r="G35">
         <v>0.828</v>
@@ -4270,28 +4270,28 @@
         <v>1.71</v>
       </c>
       <c r="M35">
-        <v>0.10772751</v>
+        <v>0.11099198</v>
       </c>
       <c r="N35">
-        <v>1.60227249</v>
+        <v>1.59900802</v>
       </c>
       <c r="O35">
-        <v>0.5607953715</v>
+        <v>0.5596528069999999</v>
       </c>
       <c r="P35">
-        <v>1.0414771185</v>
+        <v>1.039355213</v>
       </c>
       <c r="Q35">
-        <v>1.1314771185</v>
+        <v>1.129355213</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2833509129710404</v>
+        <v>0.2859959288750981</v>
       </c>
       <c r="T35">
-        <v>1.167176048354063</v>
+        <v>1.180171995926397</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.87338275989114</v>
+        <v>15.40651856107081</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1998736130575647</v>
+        <v>0.1991127644245324</v>
       </c>
       <c r="C36">
-        <v>5.283651694410924</v>
+        <v>5.251814597644302</v>
       </c>
       <c r="D36">
-        <v>6.662251694410925</v>
+        <v>6.695314597644302</v>
       </c>
       <c r="E36">
-        <v>0.7566000000000004</v>
+        <v>0.8215000000000001</v>
       </c>
       <c r="F36">
-        <v>2.2066</v>
+        <v>2.2715</v>
       </c>
       <c r="G36">
         <v>0.828</v>
@@ -4352,28 +4352,28 @@
         <v>1.71</v>
       </c>
       <c r="M36">
-        <v>0.11099198</v>
+        <v>0.11425645</v>
       </c>
       <c r="N36">
-        <v>1.59900802</v>
+        <v>1.59574355</v>
       </c>
       <c r="O36">
-        <v>0.5596528069999999</v>
+        <v>0.5585102424999999</v>
       </c>
       <c r="P36">
-        <v>1.039355213</v>
+        <v>1.0372333075</v>
       </c>
       <c r="Q36">
-        <v>1.129355213</v>
+        <v>1.1272333075</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2859959288750981</v>
+        <v>0.2887223298838961</v>
       </c>
       <c r="T36">
-        <v>1.180171995926397</v>
+        <v>1.193567818808649</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>15.40651856107081</v>
+        <v>14.96633231646878</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1991127644245324</v>
+        <v>0.1983519157915001</v>
       </c>
       <c r="C37">
-        <v>5.251814597644302</v>
+        <v>5.220307301583212</v>
       </c>
       <c r="D37">
-        <v>6.695314597644302</v>
+        <v>6.728707301583212</v>
       </c>
       <c r="E37">
-        <v>0.8215000000000001</v>
+        <v>0.8864000000000003</v>
       </c>
       <c r="F37">
-        <v>2.2715</v>
+        <v>2.3364</v>
       </c>
       <c r="G37">
         <v>0.828</v>
@@ -4434,28 +4434,28 @@
         <v>1.71</v>
       </c>
       <c r="M37">
-        <v>0.11425645</v>
+        <v>0.11752092</v>
       </c>
       <c r="N37">
-        <v>1.59574355</v>
+        <v>1.59247908</v>
       </c>
       <c r="O37">
-        <v>0.5585102424999999</v>
+        <v>0.557367678</v>
       </c>
       <c r="P37">
-        <v>1.0372333075</v>
+        <v>1.035111402</v>
       </c>
       <c r="Q37">
-        <v>1.1272333075</v>
+        <v>1.125111402</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2887223298838961</v>
+        <v>0.2915339309242189</v>
       </c>
       <c r="T37">
-        <v>1.193567818808649</v>
+        <v>1.207382261155972</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.96633231646878</v>
+        <v>14.55060086323354</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1983519157915001</v>
+        <v>0.1975910671584677</v>
       </c>
       <c r="C38">
-        <v>5.22030730158321</v>
+        <v>5.189134765579098</v>
       </c>
       <c r="D38">
-        <v>6.728707301583209</v>
+        <v>6.762434765579098</v>
       </c>
       <c r="E38">
-        <v>0.8863999999999999</v>
+        <v>0.9513</v>
       </c>
       <c r="F38">
-        <v>2.3364</v>
+        <v>2.4013</v>
       </c>
       <c r="G38">
         <v>0.828</v>
@@ -4516,28 +4516,28 @@
         <v>1.71</v>
       </c>
       <c r="M38">
-        <v>0.11752092</v>
+        <v>0.12078539</v>
       </c>
       <c r="N38">
-        <v>1.59247908</v>
+        <v>1.58921461</v>
       </c>
       <c r="O38">
-        <v>0.557367678</v>
+        <v>0.5562251134999999</v>
       </c>
       <c r="P38">
-        <v>1.035111402</v>
+        <v>1.0329894965</v>
       </c>
       <c r="Q38">
-        <v>1.125111402</v>
+        <v>1.1229894965</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2915339309242189</v>
+        <v>0.294434789140425</v>
       </c>
       <c r="T38">
-        <v>1.207382261155972</v>
+        <v>1.221635257228606</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>14.55060086323354</v>
+        <v>14.15734138044345</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1975910671584677</v>
+        <v>0.1968302185254355</v>
       </c>
       <c r="C39">
-        <v>5.189134765579098</v>
+        <v>5.158302048918785</v>
       </c>
       <c r="D39">
-        <v>6.762434765579098</v>
+        <v>6.796502048918784</v>
       </c>
       <c r="E39">
-        <v>0.9513</v>
+        <v>1.0162</v>
       </c>
       <c r="F39">
-        <v>2.4013</v>
+        <v>2.4662</v>
       </c>
       <c r="G39">
         <v>0.828</v>
@@ -4598,28 +4598,28 @@
         <v>1.71</v>
       </c>
       <c r="M39">
-        <v>0.12078539</v>
+        <v>0.12404986</v>
       </c>
       <c r="N39">
-        <v>1.58921461</v>
+        <v>1.58595014</v>
       </c>
       <c r="O39">
-        <v>0.5562251134999999</v>
+        <v>0.555082549</v>
       </c>
       <c r="P39">
-        <v>1.0329894965</v>
+        <v>1.030867591</v>
       </c>
       <c r="Q39">
-        <v>1.1229894965</v>
+        <v>1.120867591</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.294434789140425</v>
+        <v>0.2974292234281217</v>
       </c>
       <c r="T39">
-        <v>1.221635257228606</v>
+        <v>1.236348027368099</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>14.15734138044345</v>
+        <v>13.78477976516862</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1968302185254355</v>
+        <v>0.1960693698924031</v>
       </c>
       <c r="C40">
-        <v>5.158302048918785</v>
+        <v>5.127814313354469</v>
       </c>
       <c r="D40">
-        <v>6.796502048918784</v>
+        <v>6.830914313354469</v>
       </c>
       <c r="E40">
-        <v>1.0162</v>
+        <v>1.0811</v>
       </c>
       <c r="F40">
-        <v>2.4662</v>
+        <v>2.5311</v>
       </c>
       <c r="G40">
         <v>0.828</v>
@@ -4680,28 +4680,28 @@
         <v>1.71</v>
       </c>
       <c r="M40">
-        <v>0.12404986</v>
+        <v>0.12731433</v>
       </c>
       <c r="N40">
-        <v>1.58595014</v>
+        <v>1.58268567</v>
       </c>
       <c r="O40">
-        <v>0.555082549</v>
+        <v>0.5539399844999999</v>
       </c>
       <c r="P40">
-        <v>1.030867591</v>
+        <v>1.0287456855</v>
       </c>
       <c r="Q40">
-        <v>1.120867591</v>
+        <v>1.1187456855</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2974292234281217</v>
+        <v>0.3005218358891855</v>
       </c>
       <c r="T40">
-        <v>1.236348027368099</v>
+        <v>1.251543183413805</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.78477976516862</v>
+        <v>13.43132387375404</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1960693698924031</v>
+        <v>0.1953085212593708</v>
       </c>
       <c r="C41">
-        <v>5.127814313354469</v>
+        <v>5.097676825710941</v>
       </c>
       <c r="D41">
-        <v>6.830914313354469</v>
+        <v>6.865676825710941</v>
       </c>
       <c r="E41">
-        <v>1.0811</v>
+        <v>1.146</v>
       </c>
       <c r="F41">
-        <v>2.5311</v>
+        <v>2.596</v>
       </c>
       <c r="G41">
         <v>0.828</v>
@@ -4762,28 +4762,28 @@
         <v>1.71</v>
       </c>
       <c r="M41">
-        <v>0.12731433</v>
+        <v>0.1305788</v>
       </c>
       <c r="N41">
-        <v>1.58268567</v>
+        <v>1.5794212</v>
       </c>
       <c r="O41">
-        <v>0.5539399844999999</v>
+        <v>0.55279742</v>
       </c>
       <c r="P41">
-        <v>1.0287456855</v>
+        <v>1.02662378</v>
       </c>
       <c r="Q41">
-        <v>1.1187456855</v>
+        <v>1.11662378</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3005218358891855</v>
+        <v>0.3037175354322847</v>
       </c>
       <c r="T41">
-        <v>1.251543183413805</v>
+        <v>1.267244844661035</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>13.43132387375404</v>
+        <v>13.09554077691019</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1953085212593708</v>
+        <v>0.1949474226263385</v>
       </c>
       <c r="C42">
-        <v>5.097676825710941</v>
+        <v>5.049399214974866</v>
       </c>
       <c r="D42">
-        <v>6.865676825710941</v>
+        <v>6.882299214974865</v>
       </c>
       <c r="E42">
-        <v>1.146</v>
+        <v>1.2109</v>
       </c>
       <c r="F42">
-        <v>2.596</v>
+        <v>2.6609</v>
       </c>
       <c r="G42">
         <v>0.828</v>
@@ -4844,45 +4844,45 @@
         <v>1.71</v>
       </c>
       <c r="M42">
-        <v>0.1305788</v>
+        <v>0.13783462</v>
       </c>
       <c r="N42">
-        <v>1.5794212</v>
+        <v>1.57216538</v>
       </c>
       <c r="O42">
-        <v>0.55279742</v>
+        <v>0.5502578829999999</v>
       </c>
       <c r="P42">
-        <v>1.02662378</v>
+        <v>1.021907497</v>
       </c>
       <c r="Q42">
-        <v>1.11662378</v>
+        <v>1.111907497</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3037175354322847</v>
+        <v>0.3070215637734551</v>
       </c>
       <c r="T42">
-        <v>1.267244844661035</v>
+        <v>1.283478765611561</v>
       </c>
       <c r="U42">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V42">
         <v>0.35</v>
       </c>
       <c r="W42">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y42">
-        <v>13.09554077691019</v>
+        <v>12.40617197624225</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1949474226263385</v>
+        <v>0.1941963239933061</v>
       </c>
       <c r="C43">
-        <v>5.049399214974866</v>
+        <v>5.019333538315115</v>
       </c>
       <c r="D43">
-        <v>6.882299214974865</v>
+        <v>6.917133538315115</v>
       </c>
       <c r="E43">
-        <v>1.2109</v>
+        <v>1.2758</v>
       </c>
       <c r="F43">
-        <v>2.6609</v>
+        <v>2.7258</v>
       </c>
       <c r="G43">
         <v>0.828</v>
@@ -4926,28 +4926,28 @@
         <v>1.71</v>
       </c>
       <c r="M43">
-        <v>0.13783462</v>
+        <v>0.14119644</v>
       </c>
       <c r="N43">
-        <v>1.57216538</v>
+        <v>1.56880356</v>
       </c>
       <c r="O43">
-        <v>0.5502578829999999</v>
+        <v>0.549081246</v>
       </c>
       <c r="P43">
-        <v>1.021907497</v>
+        <v>1.019722314</v>
       </c>
       <c r="Q43">
-        <v>1.111907497</v>
+        <v>1.109722314</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3070215637734551</v>
+        <v>0.3104395241263899</v>
       </c>
       <c r="T43">
-        <v>1.283478765611561</v>
+        <v>1.300272476939691</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>12.40617197624225</v>
+        <v>12.11078692918887</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1941963239933062</v>
+        <v>0.1934452253602739</v>
       </c>
       <c r="C44">
-        <v>5.019333538315113</v>
+        <v>4.989622278976741</v>
       </c>
       <c r="D44">
-        <v>6.917133538315112</v>
+        <v>6.952322278976741</v>
       </c>
       <c r="E44">
-        <v>1.2758</v>
+        <v>1.3407</v>
       </c>
       <c r="F44">
-        <v>2.7258</v>
+        <v>2.7907</v>
       </c>
       <c r="G44">
         <v>0.828</v>
@@ -5008,28 +5008,28 @@
         <v>1.71</v>
       </c>
       <c r="M44">
-        <v>0.14119644</v>
+        <v>0.14455826</v>
       </c>
       <c r="N44">
-        <v>1.56880356</v>
+        <v>1.56544174</v>
       </c>
       <c r="O44">
-        <v>0.549081246</v>
+        <v>0.5479046089999999</v>
       </c>
       <c r="P44">
-        <v>1.019722314</v>
+        <v>1.017537131</v>
       </c>
       <c r="Q44">
-        <v>1.109722314</v>
+        <v>1.107537131</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3104395241263899</v>
+        <v>0.3139774129127612</v>
       </c>
       <c r="T44">
-        <v>1.300272476939691</v>
+        <v>1.317655441296878</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>12.11078692918887</v>
+        <v>11.82914072153331</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1934452253602739</v>
+        <v>0.1926941267272415</v>
       </c>
       <c r="C45">
-        <v>4.989622278976741</v>
+        <v>4.960270873576689</v>
       </c>
       <c r="D45">
-        <v>6.952322278976741</v>
+        <v>6.987870873576688</v>
       </c>
       <c r="E45">
-        <v>1.3407</v>
+        <v>1.4056</v>
       </c>
       <c r="F45">
-        <v>2.7907</v>
+        <v>2.8556</v>
       </c>
       <c r="G45">
         <v>0.828</v>
@@ -5090,28 +5090,28 @@
         <v>1.71</v>
       </c>
       <c r="M45">
-        <v>0.14455826</v>
+        <v>0.14792008</v>
       </c>
       <c r="N45">
-        <v>1.56544174</v>
+        <v>1.56207992</v>
       </c>
       <c r="O45">
-        <v>0.5479046089999999</v>
+        <v>0.5467279719999999</v>
       </c>
       <c r="P45">
-        <v>1.017537131</v>
+        <v>1.015351948</v>
       </c>
       <c r="Q45">
-        <v>1.107537131</v>
+        <v>1.105351948</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3139774129127612</v>
+        <v>0.3176416548700741</v>
       </c>
       <c r="T45">
-        <v>1.317655441296878</v>
+        <v>1.335659225809679</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.82914072153331</v>
+        <v>11.56029661422574</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1926941267272415</v>
+        <v>0.1919430280942092</v>
       </c>
       <c r="C46">
-        <v>4.960270873576689</v>
+        <v>4.931284870497336</v>
       </c>
       <c r="D46">
-        <v>6.987870873576688</v>
+        <v>7.023784870497336</v>
       </c>
       <c r="E46">
-        <v>1.4056</v>
+        <v>1.4705</v>
       </c>
       <c r="F46">
-        <v>2.8556</v>
+        <v>2.9205</v>
       </c>
       <c r="G46">
         <v>0.828</v>
@@ -5172,28 +5172,28 @@
         <v>1.71</v>
       </c>
       <c r="M46">
-        <v>0.14792008</v>
+        <v>0.1512819</v>
       </c>
       <c r="N46">
-        <v>1.56207992</v>
+        <v>1.5587181</v>
       </c>
       <c r="O46">
-        <v>0.5467279719999999</v>
+        <v>0.545551335</v>
       </c>
       <c r="P46">
-        <v>1.015351948</v>
+        <v>1.013166765</v>
       </c>
       <c r="Q46">
-        <v>1.105351948</v>
+        <v>1.103166765</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3176416548700741</v>
+        <v>0.3214391419894713</v>
       </c>
       <c r="T46">
-        <v>1.335659225809679</v>
+        <v>1.354317693395673</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.56029661422574</v>
+        <v>11.30340113390961</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1919430280942092</v>
+        <v>0.1911919294611769</v>
       </c>
       <c r="C47">
-        <v>4.931284870497336</v>
+        <v>4.902669932773454</v>
       </c>
       <c r="D47">
-        <v>7.023784870497336</v>
+        <v>7.060069932773454</v>
       </c>
       <c r="E47">
-        <v>1.4705</v>
+        <v>1.5354</v>
       </c>
       <c r="F47">
-        <v>2.9205</v>
+        <v>2.9854</v>
       </c>
       <c r="G47">
         <v>0.828</v>
@@ -5254,28 +5254,28 @@
         <v>1.71</v>
       </c>
       <c r="M47">
-        <v>0.1512819</v>
+        <v>0.15464372</v>
       </c>
       <c r="N47">
-        <v>1.5587181</v>
+        <v>1.55535628</v>
       </c>
       <c r="O47">
-        <v>0.545551335</v>
+        <v>0.5443746979999999</v>
       </c>
       <c r="P47">
-        <v>1.013166765</v>
+        <v>1.010981582</v>
       </c>
       <c r="Q47">
-        <v>1.103166765</v>
+        <v>1.100981582</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3214391419894713</v>
+        <v>0.3253772767799571</v>
       </c>
       <c r="T47">
-        <v>1.354317693395673</v>
+        <v>1.373667215336703</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.30340113390961</v>
+        <v>11.05767502230288</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1911919294611769</v>
+        <v>0.1904408308281446</v>
       </c>
       <c r="C48">
-        <v>4.902669932773454</v>
+        <v>4.87443184106904</v>
       </c>
       <c r="D48">
-        <v>7.060069932773454</v>
+        <v>7.09673184106904</v>
       </c>
       <c r="E48">
-        <v>1.5354</v>
+        <v>1.6003</v>
       </c>
       <c r="F48">
-        <v>2.9854</v>
+        <v>3.0503</v>
       </c>
       <c r="G48">
         <v>0.828</v>
@@ -5336,28 +5336,28 @@
         <v>1.71</v>
       </c>
       <c r="M48">
-        <v>0.15464372</v>
+        <v>0.15800554</v>
       </c>
       <c r="N48">
-        <v>1.55535628</v>
+        <v>1.55199446</v>
       </c>
       <c r="O48">
-        <v>0.5443746979999999</v>
+        <v>0.5431980609999999</v>
       </c>
       <c r="P48">
-        <v>1.010981582</v>
+        <v>1.008796399</v>
       </c>
       <c r="Q48">
-        <v>1.100981582</v>
+        <v>1.098796399</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3253772767799571</v>
+        <v>0.3294640204304614</v>
       </c>
       <c r="T48">
-        <v>1.373667215336703</v>
+        <v>1.393746907917018</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>11.05767502230288</v>
+        <v>10.82240534097728</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1904408308281446</v>
+        <v>0.1896897321951122</v>
       </c>
       <c r="C49">
-        <v>4.87443184106904</v>
+        <v>4.846576496747433</v>
       </c>
       <c r="D49">
-        <v>7.09673184106904</v>
+        <v>7.133776496747433</v>
       </c>
       <c r="E49">
-        <v>1.6003</v>
+        <v>1.6652</v>
       </c>
       <c r="F49">
-        <v>3.0503</v>
+        <v>3.1152</v>
       </c>
       <c r="G49">
         <v>0.828</v>
@@ -5418,28 +5418,28 @@
         <v>1.71</v>
       </c>
       <c r="M49">
-        <v>0.15800554</v>
+        <v>0.16136736</v>
       </c>
       <c r="N49">
-        <v>1.55199446</v>
+        <v>1.54863264</v>
       </c>
       <c r="O49">
-        <v>0.5431980609999999</v>
+        <v>0.542021424</v>
       </c>
       <c r="P49">
-        <v>1.008796399</v>
+        <v>1.006611216</v>
       </c>
       <c r="Q49">
-        <v>1.098796399</v>
+        <v>1.096611216</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3294640204304614</v>
+        <v>0.3337079465290619</v>
       </c>
       <c r="T49">
-        <v>1.393746907917018</v>
+        <v>1.414598896365806</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.82240534097728</v>
+        <v>10.59693856304026</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1896897321951122</v>
+        <v>0.1889386335620799</v>
       </c>
       <c r="C50">
-        <v>4.846576496747433</v>
+        <v>4.819109925038065</v>
       </c>
       <c r="D50">
-        <v>7.133776496747433</v>
+        <v>7.171209925038064</v>
       </c>
       <c r="E50">
-        <v>1.6652</v>
+        <v>1.7301</v>
       </c>
       <c r="F50">
-        <v>3.1152</v>
+        <v>3.1801</v>
       </c>
       <c r="G50">
         <v>0.828</v>
@@ -5500,28 +5500,28 @@
         <v>1.71</v>
       </c>
       <c r="M50">
-        <v>0.16136736</v>
+        <v>0.16472918</v>
       </c>
       <c r="N50">
-        <v>1.54863264</v>
+        <v>1.54527082</v>
       </c>
       <c r="O50">
-        <v>0.542021424</v>
+        <v>0.5408447869999999</v>
       </c>
       <c r="P50">
-        <v>1.006611216</v>
+        <v>1.004426033</v>
       </c>
       <c r="Q50">
-        <v>1.096611216</v>
+        <v>1.094426033</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3337079465290619</v>
+        <v>0.3381183011021174</v>
       </c>
       <c r="T50">
-        <v>1.414598896365806</v>
+        <v>1.436268609851802</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.59693856304026</v>
+        <v>10.38067451073331</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1889386335620799</v>
+        <v>0.1881875349290476</v>
       </c>
       <c r="C51">
-        <v>4.819109925038065</v>
+        <v>4.792038278303454</v>
       </c>
       <c r="D51">
-        <v>7.171209925038064</v>
+        <v>7.209038278303454</v>
       </c>
       <c r="E51">
-        <v>1.7301</v>
+        <v>1.795</v>
       </c>
       <c r="F51">
-        <v>3.1801</v>
+        <v>3.245</v>
       </c>
       <c r="G51">
         <v>0.828</v>
@@ -5582,28 +5582,28 @@
         <v>1.71</v>
       </c>
       <c r="M51">
-        <v>0.16472918</v>
+        <v>0.168091</v>
       </c>
       <c r="N51">
-        <v>1.54527082</v>
+        <v>1.541909</v>
       </c>
       <c r="O51">
-        <v>0.5408447869999999</v>
+        <v>0.5396681499999999</v>
       </c>
       <c r="P51">
-        <v>1.004426033</v>
+        <v>1.00224085</v>
       </c>
       <c r="Q51">
-        <v>1.094426033</v>
+        <v>1.09224085</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3381183011021174</v>
+        <v>0.3427050698580951</v>
       </c>
       <c r="T51">
-        <v>1.436268609851802</v>
+        <v>1.458805111877238</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.38067451073331</v>
+        <v>10.17306102051865</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1881875349290476</v>
+        <v>0.1874364362960153</v>
       </c>
       <c r="C52">
-        <v>4.792038278303454</v>
+        <v>4.765367839410136</v>
       </c>
       <c r="D52">
-        <v>7.209038278303454</v>
+        <v>7.247267839410136</v>
       </c>
       <c r="E52">
-        <v>1.795</v>
+        <v>1.8599</v>
       </c>
       <c r="F52">
-        <v>3.245</v>
+        <v>3.3099</v>
       </c>
       <c r="G52">
         <v>0.828</v>
@@ -5664,28 +5664,28 @@
         <v>1.71</v>
       </c>
       <c r="M52">
-        <v>0.168091</v>
+        <v>0.17145282</v>
       </c>
       <c r="N52">
-        <v>1.541909</v>
+        <v>1.53854718</v>
       </c>
       <c r="O52">
-        <v>0.5396681499999999</v>
+        <v>0.538491513</v>
       </c>
       <c r="P52">
-        <v>1.00224085</v>
+        <v>1.000055667</v>
       </c>
       <c r="Q52">
-        <v>1.09224085</v>
+        <v>1.090055667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3427050698580951</v>
+        <v>0.3474790536653373</v>
       </c>
       <c r="T52">
-        <v>1.458805111877238</v>
+        <v>1.482261471128202</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>10.17306102051865</v>
+        <v>9.973589235802596</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1874364362960153</v>
+        <v>0.1872599376629829</v>
       </c>
       <c r="C53">
-        <v>4.765367839410136</v>
+        <v>4.709510207786703</v>
       </c>
       <c r="D53">
-        <v>7.247267839410136</v>
+        <v>7.256310207786703</v>
       </c>
       <c r="E53">
-        <v>1.8599</v>
+        <v>1.9248</v>
       </c>
       <c r="F53">
-        <v>3.3099</v>
+        <v>3.3748</v>
       </c>
       <c r="G53">
         <v>0.828</v>
@@ -5746,45 +5746,45 @@
         <v>1.71</v>
       </c>
       <c r="M53">
-        <v>0.17145282</v>
+        <v>0.1805518</v>
       </c>
       <c r="N53">
-        <v>1.53854718</v>
+        <v>1.5294482</v>
       </c>
       <c r="O53">
-        <v>0.538491513</v>
+        <v>0.53530687</v>
       </c>
       <c r="P53">
-        <v>1.000055667</v>
+        <v>0.99414133</v>
       </c>
       <c r="Q53">
-        <v>1.090055667</v>
+        <v>1.08414133</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3474790536653373</v>
+        <v>0.3524519534645478</v>
       </c>
       <c r="T53">
-        <v>1.482261471128202</v>
+        <v>1.506695178681289</v>
       </c>
       <c r="U53">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V53">
         <v>0.35</v>
       </c>
       <c r="W53">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>9.973589235802596</v>
+        <v>9.47096622686675</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1872599376629829</v>
+        <v>0.1865198890299506</v>
       </c>
       <c r="C54">
-        <v>4.709510207786703</v>
+        <v>4.682771284285193</v>
       </c>
       <c r="D54">
-        <v>7.256310207786703</v>
+        <v>7.294471284285194</v>
       </c>
       <c r="E54">
-        <v>1.9248</v>
+        <v>1.9897</v>
       </c>
       <c r="F54">
-        <v>3.3748</v>
+        <v>3.4397</v>
       </c>
       <c r="G54">
         <v>0.828</v>
@@ -5828,28 +5828,28 @@
         <v>1.71</v>
       </c>
       <c r="M54">
-        <v>0.1805518</v>
+        <v>0.18402395</v>
       </c>
       <c r="N54">
-        <v>1.5294482</v>
+        <v>1.52597605</v>
       </c>
       <c r="O54">
-        <v>0.53530687</v>
+        <v>0.5340916174999999</v>
       </c>
       <c r="P54">
-        <v>0.99414133</v>
+        <v>0.9918844325</v>
       </c>
       <c r="Q54">
-        <v>1.08414133</v>
+        <v>1.0818844325</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3524519534645478</v>
+        <v>0.3576364660211716</v>
       </c>
       <c r="T54">
-        <v>1.506695178681289</v>
+        <v>1.532168618470678</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.47096622686675</v>
+        <v>9.29226875088813</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1865198890299506</v>
+        <v>0.1857798403969183</v>
       </c>
       <c r="C55">
-        <v>4.682771284285193</v>
+        <v>4.656435862493899</v>
       </c>
       <c r="D55">
-        <v>7.294471284285194</v>
+        <v>7.333035862493898</v>
       </c>
       <c r="E55">
-        <v>1.9897</v>
+        <v>2.054600000000001</v>
       </c>
       <c r="F55">
-        <v>3.4397</v>
+        <v>3.5046</v>
       </c>
       <c r="G55">
         <v>0.828</v>
@@ -5910,28 +5910,28 @@
         <v>1.71</v>
       </c>
       <c r="M55">
-        <v>0.18402395</v>
+        <v>0.1874961</v>
       </c>
       <c r="N55">
-        <v>1.52597605</v>
+        <v>1.5225039</v>
       </c>
       <c r="O55">
-        <v>0.5340916174999999</v>
+        <v>0.532876365</v>
       </c>
       <c r="P55">
-        <v>0.9918844325</v>
+        <v>0.989627535</v>
       </c>
       <c r="Q55">
-        <v>1.0818844325</v>
+        <v>1.079627535</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3576364660211716</v>
+        <v>0.3630463921672137</v>
       </c>
       <c r="T55">
-        <v>1.532168618470678</v>
+        <v>1.558749599120474</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>9.29226875088813</v>
+        <v>9.120189699945758</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1857798403969183</v>
+        <v>0.185039791763886</v>
       </c>
       <c r="C56">
-        <v>4.656435862493899</v>
+        <v>4.630510376153167</v>
       </c>
       <c r="D56">
-        <v>7.333035862493898</v>
+        <v>7.372010376153169</v>
       </c>
       <c r="E56">
-        <v>2.054600000000001</v>
+        <v>2.1195</v>
       </c>
       <c r="F56">
-        <v>3.5046</v>
+        <v>3.569500000000001</v>
       </c>
       <c r="G56">
         <v>0.828</v>
@@ -5992,28 +5992,28 @@
         <v>1.71</v>
       </c>
       <c r="M56">
-        <v>0.1874961</v>
+        <v>0.19096825</v>
       </c>
       <c r="N56">
-        <v>1.5225039</v>
+        <v>1.51903175</v>
       </c>
       <c r="O56">
-        <v>0.532876365</v>
+        <v>0.5316611124999999</v>
       </c>
       <c r="P56">
-        <v>0.989627535</v>
+        <v>0.9873706375</v>
       </c>
       <c r="Q56">
-        <v>1.079627535</v>
+        <v>1.0773706375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3630463921672137</v>
+        <v>0.3686967594753022</v>
       </c>
       <c r="T56">
-        <v>1.558749599120474</v>
+        <v>1.58651195668804</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>9.120189699945758</v>
+        <v>8.954368069037653</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.185039791763886</v>
+        <v>0.1842997431308536</v>
       </c>
       <c r="C57">
-        <v>4.630510376153167</v>
+        <v>4.60500139651353</v>
       </c>
       <c r="D57">
-        <v>7.372010376153169</v>
+        <v>7.411401396513531</v>
       </c>
       <c r="E57">
-        <v>2.1195</v>
+        <v>2.1844</v>
       </c>
       <c r="F57">
-        <v>3.569500000000001</v>
+        <v>3.6344</v>
       </c>
       <c r="G57">
         <v>0.828</v>
@@ -6074,28 +6074,28 @@
         <v>1.71</v>
       </c>
       <c r="M57">
-        <v>0.19096825</v>
+        <v>0.1944404</v>
       </c>
       <c r="N57">
-        <v>1.51903175</v>
+        <v>1.5155596</v>
       </c>
       <c r="O57">
-        <v>0.5316611124999999</v>
+        <v>0.5304458599999999</v>
       </c>
       <c r="P57">
-        <v>0.9873706375</v>
+        <v>0.9851137400000001</v>
       </c>
       <c r="Q57">
-        <v>1.0773706375</v>
+        <v>1.07511374</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3686967594753022</v>
+        <v>0.374603961661031</v>
       </c>
       <c r="T57">
-        <v>1.58651195668804</v>
+        <v>1.615536239599586</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.954368069037653</v>
+        <v>8.794468639233409</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1842997431308536</v>
+        <v>0.1835596944978213</v>
       </c>
       <c r="C58">
-        <v>4.60500139651353</v>
+        <v>4.579915636029215</v>
       </c>
       <c r="D58">
-        <v>7.411401396513531</v>
+        <v>7.451215636029215</v>
       </c>
       <c r="E58">
-        <v>2.1844</v>
+        <v>2.249300000000001</v>
       </c>
       <c r="F58">
-        <v>3.6344</v>
+        <v>3.6993</v>
       </c>
       <c r="G58">
         <v>0.828</v>
@@ -6156,28 +6156,28 @@
         <v>1.71</v>
       </c>
       <c r="M58">
-        <v>0.1944404</v>
+        <v>0.19791255</v>
       </c>
       <c r="N58">
-        <v>1.5155596</v>
+        <v>1.51208745</v>
       </c>
       <c r="O58">
-        <v>0.5304458599999999</v>
+        <v>0.5292306074999999</v>
       </c>
       <c r="P58">
-        <v>0.9851137400000001</v>
+        <v>0.9828568424999999</v>
       </c>
       <c r="Q58">
-        <v>1.07511374</v>
+        <v>1.0728568425</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.374603961661031</v>
+        <v>0.3807859174367937</v>
       </c>
       <c r="T58">
-        <v>1.615536239599586</v>
+        <v>1.64591048915818</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.794468639233409</v>
+        <v>8.640179715738086</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1835596944978213</v>
+        <v>0.182819645864789</v>
       </c>
       <c r="C59">
-        <v>4.579915636029215</v>
+        <v>4.555259952171397</v>
       </c>
       <c r="D59">
-        <v>7.451215636029215</v>
+        <v>7.491459952171398</v>
       </c>
       <c r="E59">
-        <v>2.249300000000001</v>
+        <v>2.3142</v>
       </c>
       <c r="F59">
-        <v>3.6993</v>
+        <v>3.764200000000001</v>
       </c>
       <c r="G59">
         <v>0.828</v>
@@ -6238,28 +6238,28 @@
         <v>1.71</v>
       </c>
       <c r="M59">
-        <v>0.19791255</v>
+        <v>0.2013847</v>
       </c>
       <c r="N59">
-        <v>1.51208745</v>
+        <v>1.5086153</v>
       </c>
       <c r="O59">
-        <v>0.5292306074999999</v>
+        <v>0.528015355</v>
       </c>
       <c r="P59">
-        <v>0.9828568424999999</v>
+        <v>0.980599945</v>
       </c>
       <c r="Q59">
-        <v>1.0728568425</v>
+        <v>1.070599945</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3807859174367937</v>
+        <v>0.3872622520590214</v>
       </c>
       <c r="T59">
-        <v>1.64591048915818</v>
+        <v>1.677731131552899</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.640179715738086</v>
+        <v>8.491211099949499</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.182819645864789</v>
+        <v>0.1820795972317567</v>
       </c>
       <c r="C60">
-        <v>4.555259952171396</v>
+        <v>4.531041351365678</v>
       </c>
       <c r="D60">
-        <v>7.491459952171397</v>
+        <v>7.532141351365678</v>
       </c>
       <c r="E60">
-        <v>2.3142</v>
+        <v>2.3791</v>
       </c>
       <c r="F60">
-        <v>3.7642</v>
+        <v>3.8291</v>
       </c>
       <c r="G60">
         <v>0.828</v>
@@ -6320,28 +6320,28 @@
         <v>1.71</v>
       </c>
       <c r="M60">
-        <v>0.2013847</v>
+        <v>0.20485685</v>
       </c>
       <c r="N60">
-        <v>1.5086153</v>
+        <v>1.50514315</v>
       </c>
       <c r="O60">
-        <v>0.528015355</v>
+        <v>0.5268001024999999</v>
       </c>
       <c r="P60">
-        <v>0.980599945</v>
+        <v>0.9783430475</v>
       </c>
       <c r="Q60">
-        <v>1.070599945</v>
+        <v>1.0683430475</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3872622520590214</v>
+        <v>0.3940545054433089</v>
       </c>
       <c r="T60">
-        <v>1.677731131552898</v>
+        <v>1.711104000405895</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.491211099949501</v>
+        <v>8.347292267746965</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1820795972317567</v>
+        <v>0.1813395485987243</v>
       </c>
       <c r="C61">
-        <v>4.531041351365678</v>
+        <v>4.507266993058547</v>
       </c>
       <c r="D61">
-        <v>7.532141351365678</v>
+        <v>7.573266993058547</v>
       </c>
       <c r="E61">
-        <v>2.3791</v>
+        <v>2.444</v>
       </c>
       <c r="F61">
-        <v>3.8291</v>
+        <v>3.894</v>
       </c>
       <c r="G61">
         <v>0.828</v>
@@ -6402,28 +6402,28 @@
         <v>1.71</v>
       </c>
       <c r="M61">
-        <v>0.20485685</v>
+        <v>0.208329</v>
       </c>
       <c r="N61">
-        <v>1.50514315</v>
+        <v>1.501671</v>
       </c>
       <c r="O61">
-        <v>0.5268001024999999</v>
+        <v>0.52558485</v>
       </c>
       <c r="P61">
-        <v>0.9783430475</v>
+        <v>0.97608615</v>
       </c>
       <c r="Q61">
-        <v>1.0683430475</v>
+        <v>1.06608615</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3940545054433089</v>
+        <v>0.4011863714968108</v>
       </c>
       <c r="T61">
-        <v>1.711104000405895</v>
+        <v>1.746145512701542</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.347292267746965</v>
+        <v>8.208170729951181</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1813395485987243</v>
+        <v>0.180599499965692</v>
       </c>
       <c r="C62">
-        <v>4.507266993058547</v>
+        <v>4.483944193917809</v>
       </c>
       <c r="D62">
-        <v>7.573266993058547</v>
+        <v>7.61484419391781</v>
       </c>
       <c r="E62">
-        <v>2.444</v>
+        <v>2.5089</v>
       </c>
       <c r="F62">
-        <v>3.894</v>
+        <v>3.9589</v>
       </c>
       <c r="G62">
         <v>0.828</v>
@@ -6484,28 +6484,28 @@
         <v>1.71</v>
       </c>
       <c r="M62">
-        <v>0.208329</v>
+        <v>0.21180115</v>
       </c>
       <c r="N62">
-        <v>1.501671</v>
+        <v>1.49819885</v>
       </c>
       <c r="O62">
-        <v>0.52558485</v>
+        <v>0.5243695975</v>
       </c>
       <c r="P62">
-        <v>0.97608615</v>
+        <v>0.9738292525000001</v>
       </c>
       <c r="Q62">
-        <v>1.06608615</v>
+        <v>1.0638292525</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4011863714968108</v>
+        <v>0.4086839742710052</v>
       </c>
       <c r="T62">
-        <v>1.746145512701542</v>
+        <v>1.782984025627735</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.208170729951181</v>
+        <v>8.073610554050344</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.180599499965692</v>
+        <v>0.1798594513326597</v>
       </c>
       <c r="C63">
-        <v>4.483944193917809</v>
+        <v>4.461080432172126</v>
       </c>
       <c r="D63">
-        <v>7.61484419391781</v>
+        <v>7.656880432172126</v>
       </c>
       <c r="E63">
-        <v>2.5089</v>
+        <v>2.5738</v>
       </c>
       <c r="F63">
-        <v>3.9589</v>
+        <v>4.0238</v>
       </c>
       <c r="G63">
         <v>0.828</v>
@@ -6566,28 +6566,28 @@
         <v>1.71</v>
       </c>
       <c r="M63">
-        <v>0.21180115</v>
+        <v>0.2152733</v>
       </c>
       <c r="N63">
-        <v>1.49819885</v>
+        <v>1.4947267</v>
       </c>
       <c r="O63">
-        <v>0.5243695975</v>
+        <v>0.5231543449999999</v>
       </c>
       <c r="P63">
-        <v>0.9738292525000001</v>
+        <v>0.9715723550000001</v>
       </c>
       <c r="Q63">
-        <v>1.0638292525</v>
+        <v>1.061572355</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4086839742710052</v>
+        <v>0.4165761877175256</v>
       </c>
       <c r="T63">
-        <v>1.782984025627735</v>
+        <v>1.821761407655307</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.073610554050344</v>
+        <v>7.943391028985014</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1798594513326597</v>
+        <v>0.1791194026996274</v>
       </c>
       <c r="C64">
-        <v>4.461080432172126</v>
+        <v>4.438683352095102</v>
       </c>
       <c r="D64">
-        <v>7.656880432172126</v>
+        <v>7.699383352095102</v>
       </c>
       <c r="E64">
-        <v>2.5738</v>
+        <v>2.6387</v>
       </c>
       <c r="F64">
-        <v>4.0238</v>
+        <v>4.0887</v>
       </c>
       <c r="G64">
         <v>0.828</v>
@@ -6648,28 +6648,28 @@
         <v>1.71</v>
       </c>
       <c r="M64">
-        <v>0.2152733</v>
+        <v>0.21874545</v>
       </c>
       <c r="N64">
-        <v>1.4947267</v>
+        <v>1.49125455</v>
       </c>
       <c r="O64">
-        <v>0.5231543449999999</v>
+        <v>0.5219390924999999</v>
       </c>
       <c r="P64">
-        <v>0.9715723550000001</v>
+        <v>0.9693154574999999</v>
       </c>
       <c r="Q64">
-        <v>1.061572355</v>
+        <v>1.0593154575</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4165761877175256</v>
+        <v>0.4248950072962902</v>
       </c>
       <c r="T64">
-        <v>1.821761407655307</v>
+        <v>1.862634864387071</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.943391028985014</v>
+        <v>7.817305457096364</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1791194026996274</v>
+        <v>0.1783793540665951</v>
       </c>
       <c r="C65">
-        <v>4.438683352095102</v>
+        <v>4.416760768639517</v>
       </c>
       <c r="D65">
-        <v>7.699383352095102</v>
+        <v>7.742360768639517</v>
       </c>
       <c r="E65">
-        <v>2.6387</v>
+        <v>2.7036</v>
       </c>
       <c r="F65">
-        <v>4.0887</v>
+        <v>4.1536</v>
       </c>
       <c r="G65">
         <v>0.828</v>
@@ -6730,28 +6730,28 @@
         <v>1.71</v>
       </c>
       <c r="M65">
-        <v>0.21874545</v>
+        <v>0.2222176</v>
       </c>
       <c r="N65">
-        <v>1.49125455</v>
+        <v>1.4877824</v>
       </c>
       <c r="O65">
-        <v>0.5219390924999999</v>
+        <v>0.5207238399999999</v>
       </c>
       <c r="P65">
-        <v>0.9693154574999999</v>
+        <v>0.96705856</v>
       </c>
       <c r="Q65">
-        <v>1.0593154575</v>
+        <v>1.05705856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4248950072962902</v>
+        <v>0.4336759835183197</v>
       </c>
       <c r="T65">
-        <v>1.862634864387071</v>
+        <v>1.905779068715045</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.817305457096364</v>
+        <v>7.695160059329234</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1783793540665951</v>
+        <v>0.1779773054335627</v>
       </c>
       <c r="C66">
-        <v>4.416760768639517</v>
+        <v>4.375410995762579</v>
       </c>
       <c r="D66">
-        <v>7.742360768639517</v>
+        <v>7.765910995762579</v>
       </c>
       <c r="E66">
-        <v>2.7036</v>
+        <v>2.7685</v>
       </c>
       <c r="F66">
-        <v>4.1536</v>
+        <v>4.218500000000001</v>
       </c>
       <c r="G66">
         <v>0.828</v>
@@ -6812,45 +6812,45 @@
         <v>1.71</v>
       </c>
       <c r="M66">
-        <v>0.2222176</v>
+        <v>0.22906455</v>
       </c>
       <c r="N66">
-        <v>1.4877824</v>
+        <v>1.48093545</v>
       </c>
       <c r="O66">
-        <v>0.5207238399999999</v>
+        <v>0.5183274074999999</v>
       </c>
       <c r="P66">
-        <v>0.96705856</v>
+        <v>0.9626080425000001</v>
       </c>
       <c r="Q66">
-        <v>1.05705856</v>
+        <v>1.0526080425</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4336759835183197</v>
+        <v>0.4429587298101793</v>
       </c>
       <c r="T66">
-        <v>1.905779068715045</v>
+        <v>1.951388656147474</v>
       </c>
       <c r="U66">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V66">
         <v>0.35</v>
       </c>
       <c r="W66">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y66">
-        <v>7.695160059329234</v>
+        <v>7.465144650274343</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1779773054335627</v>
+        <v>0.1772424568005304</v>
       </c>
       <c r="C67">
-        <v>4.375410995762579</v>
+        <v>4.353927477912995</v>
       </c>
       <c r="D67">
-        <v>7.765910995762579</v>
+        <v>7.809327477912996</v>
       </c>
       <c r="E67">
-        <v>2.7685</v>
+        <v>2.8334</v>
       </c>
       <c r="F67">
-        <v>4.218500000000001</v>
+        <v>4.2834</v>
       </c>
       <c r="G67">
         <v>0.828</v>
@@ -6894,28 +6894,28 @@
         <v>1.71</v>
       </c>
       <c r="M67">
-        <v>0.22906455</v>
+        <v>0.23258862</v>
       </c>
       <c r="N67">
-        <v>1.48093545</v>
+        <v>1.47741138</v>
       </c>
       <c r="O67">
-        <v>0.5183274074999999</v>
+        <v>0.517093983</v>
       </c>
       <c r="P67">
-        <v>0.9626080425000001</v>
+        <v>0.960317397</v>
       </c>
       <c r="Q67">
-        <v>1.0526080425</v>
+        <v>1.050317397</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4429587298101793</v>
+        <v>0.45278752000156</v>
       </c>
       <c r="T67">
-        <v>1.951388656147474</v>
+        <v>1.999681160487693</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.465144650274343</v>
+        <v>7.352036397997459</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1772424568005304</v>
+        <v>0.1765076081674981</v>
       </c>
       <c r="C68">
-        <v>4.353927477912995</v>
+        <v>4.33293214193754</v>
       </c>
       <c r="D68">
-        <v>7.809327477912996</v>
+        <v>7.853232141937541</v>
       </c>
       <c r="E68">
-        <v>2.8334</v>
+        <v>2.8983</v>
       </c>
       <c r="F68">
-        <v>4.2834</v>
+        <v>4.3483</v>
       </c>
       <c r="G68">
         <v>0.828</v>
@@ -6976,28 +6976,28 @@
         <v>1.71</v>
       </c>
       <c r="M68">
-        <v>0.23258862</v>
+        <v>0.23611269</v>
       </c>
       <c r="N68">
-        <v>1.47741138</v>
+        <v>1.47388731</v>
       </c>
       <c r="O68">
-        <v>0.517093983</v>
+        <v>0.5158605584999999</v>
       </c>
       <c r="P68">
-        <v>0.960317397</v>
+        <v>0.9580267514999999</v>
       </c>
       <c r="Q68">
-        <v>1.050317397</v>
+        <v>1.0480267515</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.45278752000156</v>
+        <v>0.4632119944469639</v>
       </c>
       <c r="T68">
-        <v>1.999681160487693</v>
+        <v>2.050900483272775</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.352036397997459</v>
+        <v>7.242304511460183</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1765076081674981</v>
+        <v>0.1757727595344658</v>
       </c>
       <c r="C69">
-        <v>4.33293214193754</v>
+        <v>4.312433268181675</v>
       </c>
       <c r="D69">
-        <v>7.853232141937541</v>
+        <v>7.897633268181676</v>
       </c>
       <c r="E69">
-        <v>2.8983</v>
+        <v>2.963200000000001</v>
       </c>
       <c r="F69">
-        <v>4.3483</v>
+        <v>4.413200000000001</v>
       </c>
       <c r="G69">
         <v>0.828</v>
@@ -7058,28 +7058,28 @@
         <v>1.71</v>
       </c>
       <c r="M69">
-        <v>0.23611269</v>
+        <v>0.23963676</v>
       </c>
       <c r="N69">
-        <v>1.47388731</v>
+        <v>1.47036324</v>
       </c>
       <c r="O69">
-        <v>0.5158605584999999</v>
+        <v>0.5146271339999999</v>
       </c>
       <c r="P69">
-        <v>0.9580267514999999</v>
+        <v>0.955736106</v>
       </c>
       <c r="Q69">
-        <v>1.0480267515</v>
+        <v>1.045736106</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4632119944469639</v>
+        <v>0.4742879985452055</v>
       </c>
       <c r="T69">
-        <v>2.050900483272775</v>
+        <v>2.105321013731923</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.242304511460183</v>
+        <v>7.135800033350475</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1757727595344658</v>
+        <v>0.1750379109014334</v>
       </c>
       <c r="C70">
-        <v>4.312433268181675</v>
+        <v>4.292439325319509</v>
       </c>
       <c r="D70">
-        <v>7.897633268181676</v>
+        <v>7.942539325319509</v>
       </c>
       <c r="E70">
-        <v>2.963200000000001</v>
+        <v>3.0281</v>
       </c>
       <c r="F70">
-        <v>4.413200000000001</v>
+        <v>4.4781</v>
       </c>
       <c r="G70">
         <v>0.828</v>
@@ -7140,28 +7140,28 @@
         <v>1.71</v>
       </c>
       <c r="M70">
-        <v>0.23963676</v>
+        <v>0.24316083</v>
       </c>
       <c r="N70">
-        <v>1.47036324</v>
+        <v>1.46683917</v>
       </c>
       <c r="O70">
-        <v>0.5146271339999999</v>
+        <v>0.5133937095</v>
       </c>
       <c r="P70">
-        <v>0.955736106</v>
+        <v>0.9534454604999999</v>
       </c>
       <c r="Q70">
-        <v>1.045736106</v>
+        <v>1.0434454605</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4742879985452055</v>
+        <v>0.4860785835530111</v>
       </c>
       <c r="T70">
-        <v>2.105321013731923</v>
+        <v>2.163252546156178</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.135800033350475</v>
+        <v>7.032382641562787</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1750379109014334</v>
+        <v>0.1743030622684011</v>
       </c>
       <c r="C71">
-        <v>4.292439325319509</v>
+        <v>4.272958975738624</v>
       </c>
       <c r="D71">
-        <v>7.942539325319509</v>
+        <v>7.987958975738625</v>
       </c>
       <c r="E71">
-        <v>3.0281</v>
+        <v>3.093</v>
       </c>
       <c r="F71">
-        <v>4.4781</v>
+        <v>4.543</v>
       </c>
       <c r="G71">
         <v>0.828</v>
@@ -7222,28 +7222,28 @@
         <v>1.71</v>
       </c>
       <c r="M71">
-        <v>0.24316083</v>
+        <v>0.2466849</v>
       </c>
       <c r="N71">
-        <v>1.46683917</v>
+        <v>1.4633151</v>
       </c>
       <c r="O71">
-        <v>0.5133937095</v>
+        <v>0.512160285</v>
       </c>
       <c r="P71">
-        <v>0.9534454604999999</v>
+        <v>0.951154815</v>
       </c>
       <c r="Q71">
-        <v>1.0434454605</v>
+        <v>1.041154815</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4860785835530111</v>
+        <v>0.4986552075613371</v>
       </c>
       <c r="T71">
-        <v>2.163252546156178</v>
+        <v>2.22504618074205</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.032382641562787</v>
+        <v>6.931920032397604</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1743030622684011</v>
+        <v>0.1735682136353688</v>
       </c>
       <c r="C72">
-        <v>4.272958975738624</v>
+        <v>4.254001081110712</v>
       </c>
       <c r="D72">
-        <v>7.987958975738625</v>
+        <v>8.033901081110713</v>
       </c>
       <c r="E72">
-        <v>3.093</v>
+        <v>3.157900000000001</v>
       </c>
       <c r="F72">
-        <v>4.543</v>
+        <v>4.607900000000001</v>
       </c>
       <c r="G72">
         <v>0.828</v>
@@ -7304,28 +7304,28 @@
         <v>1.71</v>
       </c>
       <c r="M72">
-        <v>0.2466849</v>
+        <v>0.25020897</v>
       </c>
       <c r="N72">
-        <v>1.4633151</v>
+        <v>1.45979103</v>
       </c>
       <c r="O72">
-        <v>0.512160285</v>
+        <v>0.5109268604999999</v>
       </c>
       <c r="P72">
-        <v>0.951154815</v>
+        <v>0.9488641695</v>
       </c>
       <c r="Q72">
-        <v>1.041154815</v>
+        <v>1.0388641695</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4986552075613371</v>
+        <v>0.5120991849495476</v>
       </c>
       <c r="T72">
-        <v>2.22504618074205</v>
+        <v>2.291101445299362</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.931920032397604</v>
+        <v>6.834287355884961</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1735682136353688</v>
+        <v>0.1728333650023365</v>
       </c>
       <c r="C73">
-        <v>4.254001081110713</v>
+        <v>4.235574708155563</v>
       </c>
       <c r="D73">
-        <v>8.033901081110713</v>
+        <v>8.080374708155563</v>
       </c>
       <c r="E73">
-        <v>3.1579</v>
+        <v>3.222799999999999</v>
       </c>
       <c r="F73">
-        <v>4.6079</v>
+        <v>4.6728</v>
       </c>
       <c r="G73">
         <v>0.828</v>
@@ -7386,28 +7386,28 @@
         <v>1.71</v>
       </c>
       <c r="M73">
-        <v>0.25020897</v>
+        <v>0.25373304</v>
       </c>
       <c r="N73">
-        <v>1.45979103</v>
+        <v>1.45626696</v>
       </c>
       <c r="O73">
-        <v>0.5109268604999999</v>
+        <v>0.5096934359999999</v>
       </c>
       <c r="P73">
-        <v>0.9488641695</v>
+        <v>0.9465735240000001</v>
       </c>
       <c r="Q73">
-        <v>1.0388641695</v>
+        <v>1.036573524</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5120991849495475</v>
+        <v>0.5265034464369159</v>
       </c>
       <c r="T73">
-        <v>2.291101445299361</v>
+        <v>2.361874943039338</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.834287355884963</v>
+        <v>6.739366698164339</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1728333650023365</v>
+        <v>0.1720985163693041</v>
       </c>
       <c r="C74">
-        <v>4.235574708155563</v>
+        <v>4.217689134606264</v>
       </c>
       <c r="D74">
-        <v>8.080374708155563</v>
+        <v>8.127389134606265</v>
       </c>
       <c r="E74">
-        <v>3.222799999999999</v>
+        <v>3.2877</v>
       </c>
       <c r="F74">
-        <v>4.6728</v>
+        <v>4.7377</v>
       </c>
       <c r="G74">
         <v>0.828</v>
@@ -7468,28 +7468,28 @@
         <v>1.71</v>
       </c>
       <c r="M74">
-        <v>0.25373304</v>
+        <v>0.25725711</v>
       </c>
       <c r="N74">
-        <v>1.45626696</v>
+        <v>1.45274289</v>
       </c>
       <c r="O74">
-        <v>0.5096934359999999</v>
+        <v>0.5084600115</v>
       </c>
       <c r="P74">
-        <v>0.9465735240000001</v>
+        <v>0.9442828784999999</v>
       </c>
       <c r="Q74">
-        <v>1.036573524</v>
+        <v>1.0342828785</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5265034464369159</v>
+        <v>0.5419746902566819</v>
       </c>
       <c r="T74">
-        <v>2.361874943039338</v>
+        <v>2.437890922093386</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.739366698164339</v>
+        <v>6.647046606408662</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1720985163693041</v>
+        <v>0.1713636677362718</v>
       </c>
       <c r="C75">
-        <v>4.217689134606264</v>
+        <v>4.200353855383865</v>
       </c>
       <c r="D75">
-        <v>8.127389134606265</v>
+        <v>8.174953855383865</v>
       </c>
       <c r="E75">
-        <v>3.2877</v>
+        <v>3.3526</v>
       </c>
       <c r="F75">
-        <v>4.7377</v>
+        <v>4.8026</v>
       </c>
       <c r="G75">
         <v>0.828</v>
@@ -7550,28 +7550,28 @@
         <v>1.71</v>
       </c>
       <c r="M75">
-        <v>0.25725711</v>
+        <v>0.26078118</v>
       </c>
       <c r="N75">
-        <v>1.45274289</v>
+        <v>1.44921882</v>
       </c>
       <c r="O75">
-        <v>0.5084600115</v>
+        <v>0.507226587</v>
       </c>
       <c r="P75">
-        <v>0.9442828784999999</v>
+        <v>0.941992233</v>
       </c>
       <c r="Q75">
-        <v>1.0342828785</v>
+        <v>1.031992233</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5419746902566819</v>
+        <v>0.5586360297548915</v>
       </c>
       <c r="T75">
-        <v>2.437890922093386</v>
+        <v>2.519754284151592</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.647046606408662</v>
+        <v>6.557221652268005</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1713636677362718</v>
+        <v>0.1706288191032395</v>
       </c>
       <c r="C76">
-        <v>4.200353855383865</v>
+        <v>4.183578588990155</v>
       </c>
       <c r="D76">
-        <v>8.174953855383865</v>
+        <v>8.223078588990155</v>
       </c>
       <c r="E76">
-        <v>3.3526</v>
+        <v>3.4175</v>
       </c>
       <c r="F76">
-        <v>4.8026</v>
+        <v>4.8675</v>
       </c>
       <c r="G76">
         <v>0.828</v>
@@ -7632,28 +7632,28 @@
         <v>1.71</v>
       </c>
       <c r="M76">
-        <v>0.26078118</v>
+        <v>0.26430525</v>
       </c>
       <c r="N76">
-        <v>1.44921882</v>
+        <v>1.44569475</v>
       </c>
       <c r="O76">
-        <v>0.507226587</v>
+        <v>0.5059931624999999</v>
       </c>
       <c r="P76">
-        <v>0.941992233</v>
+        <v>0.9397015875</v>
       </c>
       <c r="Q76">
-        <v>1.031992233</v>
+        <v>1.0297015875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5586360297548915</v>
+        <v>0.5766302764129579</v>
       </c>
       <c r="T76">
-        <v>2.519754284151592</v>
+        <v>2.608166715174456</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.557221652268005</v>
+        <v>6.469792030237764</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1706288191032395</v>
+        <v>0.1698939704702072</v>
       </c>
       <c r="C77">
-        <v>4.183578588990155</v>
+        <v>4.167373284127559</v>
       </c>
       <c r="D77">
-        <v>8.223078588990155</v>
+        <v>8.27177328412756</v>
       </c>
       <c r="E77">
-        <v>3.4175</v>
+        <v>3.4824</v>
       </c>
       <c r="F77">
-        <v>4.8675</v>
+        <v>4.9324</v>
       </c>
       <c r="G77">
         <v>0.828</v>
@@ -7714,28 +7714,28 @@
         <v>1.71</v>
       </c>
       <c r="M77">
-        <v>0.26430525</v>
+        <v>0.26782932</v>
       </c>
       <c r="N77">
-        <v>1.44569475</v>
+        <v>1.44217068</v>
       </c>
       <c r="O77">
-        <v>0.5059931624999999</v>
+        <v>0.504759738</v>
       </c>
       <c r="P77">
-        <v>0.9397015875</v>
+        <v>0.9374109419999999</v>
       </c>
       <c r="Q77">
-        <v>1.0297015875</v>
+        <v>1.027410942</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5766302764129579</v>
+        <v>0.5961240436258632</v>
       </c>
       <c r="T77">
-        <v>2.608166715174456</v>
+        <v>2.703946848782557</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.469792030237764</v>
+        <v>6.384663187734635</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1698939704702072</v>
+        <v>0.1691591218371748</v>
       </c>
       <c r="C78">
-        <v>4.167373284127559</v>
+        <v>4.15174812655565</v>
       </c>
       <c r="D78">
-        <v>8.27177328412756</v>
+        <v>8.321048126555651</v>
       </c>
       <c r="E78">
-        <v>3.4824</v>
+        <v>3.5473</v>
       </c>
       <c r="F78">
-        <v>4.9324</v>
+        <v>4.9973</v>
       </c>
       <c r="G78">
         <v>0.828</v>
@@ -7796,28 +7796,28 @@
         <v>1.71</v>
       </c>
       <c r="M78">
-        <v>0.26782932</v>
+        <v>0.27135339</v>
       </c>
       <c r="N78">
-        <v>1.44217068</v>
+        <v>1.43864661</v>
       </c>
       <c r="O78">
-        <v>0.504759738</v>
+        <v>0.5035263135</v>
       </c>
       <c r="P78">
-        <v>0.9374109419999999</v>
+        <v>0.9351202964999999</v>
       </c>
       <c r="Q78">
-        <v>1.027410942</v>
+        <v>1.0251202965</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5961240436258632</v>
+        <v>0.6173129210311949</v>
       </c>
       <c r="T78">
-        <v>2.703946848782557</v>
+        <v>2.808055689660928</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.384663187734635</v>
+        <v>6.301745483997822</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1691591218371748</v>
+        <v>0.1684242732041425</v>
       </c>
       <c r="C79">
-        <v>4.15174812655565</v>
+        <v>4.136713546194189</v>
       </c>
       <c r="D79">
-        <v>8.321048126555651</v>
+        <v>8.37091354619419</v>
       </c>
       <c r="E79">
-        <v>3.5473</v>
+        <v>3.612200000000001</v>
       </c>
       <c r="F79">
-        <v>4.9973</v>
+        <v>5.062200000000001</v>
       </c>
       <c r="G79">
         <v>0.828</v>
@@ -7878,28 +7878,28 @@
         <v>1.71</v>
       </c>
       <c r="M79">
-        <v>0.27135339</v>
+        <v>0.27487746</v>
       </c>
       <c r="N79">
-        <v>1.43864661</v>
+        <v>1.43512254</v>
       </c>
       <c r="O79">
-        <v>0.5035263135</v>
+        <v>0.502292889</v>
       </c>
       <c r="P79">
-        <v>0.9351202964999999</v>
+        <v>0.932829651</v>
       </c>
       <c r="Q79">
-        <v>1.0251202965</v>
+        <v>1.022829651</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6173129210311949</v>
+        <v>0.6404280600188296</v>
       </c>
       <c r="T79">
-        <v>2.808055689660928</v>
+        <v>2.921628970619151</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.301745483997822</v>
+        <v>6.22095387522862</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1684242732041425</v>
+        <v>0.1676894245711102</v>
       </c>
       <c r="C80">
-        <v>4.136713546194189</v>
+        <v>4.122280224483116</v>
       </c>
       <c r="D80">
-        <v>8.37091354619419</v>
+        <v>8.421380224483118</v>
       </c>
       <c r="E80">
-        <v>3.612200000000001</v>
+        <v>3.6771</v>
       </c>
       <c r="F80">
-        <v>5.062200000000001</v>
+        <v>5.1271</v>
       </c>
       <c r="G80">
         <v>0.828</v>
@@ -7960,28 +7960,28 @@
         <v>1.71</v>
       </c>
       <c r="M80">
-        <v>0.27487746</v>
+        <v>0.27840153</v>
       </c>
       <c r="N80">
-        <v>1.43512254</v>
+        <v>1.43159847</v>
       </c>
       <c r="O80">
-        <v>0.502292889</v>
+        <v>0.5010594644999999</v>
       </c>
       <c r="P80">
-        <v>0.932829651</v>
+        <v>0.9305390055</v>
       </c>
       <c r="Q80">
-        <v>1.022829651</v>
+        <v>1.0205390055</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6404280600188296</v>
+        <v>0.6657446408148106</v>
       </c>
       <c r="T80">
-        <v>2.921628970619151</v>
+        <v>3.046018754525777</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.22095387522862</v>
+        <v>6.142207623643447</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1676894245711102</v>
+        <v>0.1674745759380779</v>
       </c>
       <c r="C81">
-        <v>4.122280224483116</v>
+        <v>4.072250397775493</v>
       </c>
       <c r="D81">
-        <v>8.421380224483118</v>
+        <v>8.436250397775494</v>
       </c>
       <c r="E81">
-        <v>3.6771</v>
+        <v>3.742</v>
       </c>
       <c r="F81">
-        <v>5.1271</v>
+        <v>5.192</v>
       </c>
       <c r="G81">
         <v>0.828</v>
@@ -8042,45 +8042,45 @@
         <v>1.71</v>
       </c>
       <c r="M81">
-        <v>0.27840153</v>
+        <v>0.2871176</v>
       </c>
       <c r="N81">
-        <v>1.43159847</v>
+        <v>1.4228824</v>
       </c>
       <c r="O81">
-        <v>0.5010594644999999</v>
+        <v>0.49800884</v>
       </c>
       <c r="P81">
-        <v>0.9305390055</v>
+        <v>0.92487356</v>
       </c>
       <c r="Q81">
-        <v>1.0205390055</v>
+        <v>1.01487356</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6657446408148106</v>
+        <v>0.6935928796903894</v>
       </c>
       <c r="T81">
-        <v>3.046018754525777</v>
+        <v>3.182847516823065</v>
       </c>
       <c r="U81">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V81">
         <v>0.35</v>
       </c>
       <c r="W81">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>6.142207623643447</v>
+        <v>5.955747749354271</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1674745759380779</v>
+        <v>0.1667462273050455</v>
       </c>
       <c r="C82">
-        <v>4.072250397775493</v>
+        <v>4.058154226733634</v>
       </c>
       <c r="D82">
-        <v>8.436250397775494</v>
+        <v>8.487054226733635</v>
       </c>
       <c r="E82">
-        <v>3.742</v>
+        <v>3.806900000000001</v>
       </c>
       <c r="F82">
-        <v>5.192</v>
+        <v>5.256900000000001</v>
       </c>
       <c r="G82">
         <v>0.828</v>
@@ -8124,28 +8124,28 @@
         <v>1.71</v>
       </c>
       <c r="M82">
-        <v>0.2871176</v>
+        <v>0.2907065700000001</v>
       </c>
       <c r="N82">
-        <v>1.4228824</v>
+        <v>1.41929343</v>
       </c>
       <c r="O82">
-        <v>0.49800884</v>
+        <v>0.4967527005</v>
       </c>
       <c r="P82">
-        <v>0.92487356</v>
+        <v>0.9225407295</v>
       </c>
       <c r="Q82">
-        <v>1.01487356</v>
+        <v>1.0125407295</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6935928796903894</v>
+        <v>0.7243725121318187</v>
       </c>
       <c r="T82">
-        <v>3.182847516823065</v>
+        <v>3.334079306730594</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.955747749354271</v>
+        <v>5.882219999362243</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1667462273050455</v>
+        <v>0.1660178786720132</v>
       </c>
       <c r="C83">
-        <v>4.058154226733634</v>
+        <v>4.044673652968709</v>
       </c>
       <c r="D83">
-        <v>8.487054226733635</v>
+        <v>8.53847365296871</v>
       </c>
       <c r="E83">
-        <v>3.806900000000001</v>
+        <v>3.8718</v>
       </c>
       <c r="F83">
-        <v>5.256900000000001</v>
+        <v>5.321800000000001</v>
       </c>
       <c r="G83">
         <v>0.828</v>
@@ -8206,28 +8206,28 @@
         <v>1.71</v>
       </c>
       <c r="M83">
-        <v>0.2907065700000001</v>
+        <v>0.29429554</v>
       </c>
       <c r="N83">
-        <v>1.41929343</v>
+        <v>1.41570446</v>
       </c>
       <c r="O83">
-        <v>0.4967527005</v>
+        <v>0.4954965609999999</v>
       </c>
       <c r="P83">
-        <v>0.9225407295</v>
+        <v>0.920207899</v>
       </c>
       <c r="Q83">
-        <v>1.0125407295</v>
+        <v>1.010207899</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7243725121318187</v>
+        <v>0.758572103733407</v>
       </c>
       <c r="T83">
-        <v>3.334079306730594</v>
+        <v>3.50211462885007</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.882219999362243</v>
+        <v>5.810485609126118</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1660178786720132</v>
+        <v>0.1652895300389809</v>
       </c>
       <c r="C84">
-        <v>4.044673652968709</v>
+        <v>4.03181993360345</v>
       </c>
       <c r="D84">
-        <v>8.53847365296871</v>
+        <v>8.590519933603451</v>
       </c>
       <c r="E84">
-        <v>3.8718</v>
+        <v>3.9367</v>
       </c>
       <c r="F84">
-        <v>5.321800000000001</v>
+        <v>5.3867</v>
       </c>
       <c r="G84">
         <v>0.828</v>
@@ -8288,28 +8288,28 @@
         <v>1.71</v>
       </c>
       <c r="M84">
-        <v>0.29429554</v>
+        <v>0.29788451</v>
       </c>
       <c r="N84">
-        <v>1.41570446</v>
+        <v>1.41211549</v>
       </c>
       <c r="O84">
-        <v>0.4954965609999999</v>
+        <v>0.4942404214999999</v>
       </c>
       <c r="P84">
-        <v>0.920207899</v>
+        <v>0.9178750685</v>
       </c>
       <c r="Q84">
-        <v>1.010207899</v>
+        <v>1.0078750685</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.758572103733407</v>
+        <v>0.796795176699888</v>
       </c>
       <c r="T84">
-        <v>3.50211462885007</v>
+        <v>3.689918812395368</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.810485609126118</v>
+        <v>5.740479758413755</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1652895300389809</v>
+        <v>0.1645611814059486</v>
       </c>
       <c r="C85">
-        <v>4.03181993360345</v>
+        <v>4.019604601915139</v>
       </c>
       <c r="D85">
-        <v>8.590519933603451</v>
+        <v>8.643204601915141</v>
       </c>
       <c r="E85">
-        <v>3.9367</v>
+        <v>4.001600000000001</v>
       </c>
       <c r="F85">
-        <v>5.3867</v>
+        <v>5.451600000000001</v>
       </c>
       <c r="G85">
         <v>0.828</v>
@@ -8370,28 +8370,28 @@
         <v>1.71</v>
       </c>
       <c r="M85">
-        <v>0.29788451</v>
+        <v>0.3014734800000001</v>
       </c>
       <c r="N85">
-        <v>1.41211549</v>
+        <v>1.40852652</v>
       </c>
       <c r="O85">
-        <v>0.4942404214999999</v>
+        <v>0.4929842819999999</v>
       </c>
       <c r="P85">
-        <v>0.9178750685</v>
+        <v>0.915542238</v>
       </c>
       <c r="Q85">
-        <v>1.0078750685</v>
+        <v>1.005542238</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.796795176699888</v>
+        <v>0.8397961337871791</v>
       </c>
       <c r="T85">
-        <v>3.689918812395368</v>
+        <v>3.901198518883828</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.740479758413755</v>
+        <v>5.672140713670733</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1645611814059486</v>
+        <v>0.1638328327729163</v>
       </c>
       <c r="C86">
-        <v>4.019604601915142</v>
+        <v>4.008039475855978</v>
       </c>
       <c r="D86">
-        <v>8.643204601915143</v>
+        <v>8.696539475855978</v>
       </c>
       <c r="E86">
-        <v>4.0016</v>
+        <v>4.0665</v>
       </c>
       <c r="F86">
-        <v>5.4516</v>
+        <v>5.5165</v>
       </c>
       <c r="G86">
         <v>0.828</v>
@@ -8452,28 +8452,28 @@
         <v>1.71</v>
       </c>
       <c r="M86">
-        <v>0.30147348</v>
+        <v>0.30506245</v>
       </c>
       <c r="N86">
-        <v>1.40852652</v>
+        <v>1.40493755</v>
       </c>
       <c r="O86">
-        <v>0.4929842819999999</v>
+        <v>0.4917281425</v>
       </c>
       <c r="P86">
-        <v>0.915542238</v>
+        <v>0.9132094075000001</v>
       </c>
       <c r="Q86">
-        <v>1.005542238</v>
+        <v>1.0032094075</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8397961337871785</v>
+        <v>0.8885305518194417</v>
       </c>
       <c r="T86">
-        <v>3.901198518883825</v>
+        <v>4.140648852904079</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.672140713670734</v>
+        <v>5.605409646451079</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1638328327729163</v>
+        <v>0.163104484139884</v>
       </c>
       <c r="C87">
-        <v>4.008039475855978</v>
+        <v>3.997136666890876</v>
       </c>
       <c r="D87">
-        <v>8.696539475855978</v>
+        <v>8.750536666890877</v>
       </c>
       <c r="E87">
-        <v>4.0665</v>
+        <v>4.1314</v>
       </c>
       <c r="F87">
-        <v>5.5165</v>
+        <v>5.5814</v>
       </c>
       <c r="G87">
         <v>0.828</v>
@@ -8534,28 +8534,28 @@
         <v>1.71</v>
       </c>
       <c r="M87">
-        <v>0.30506245</v>
+        <v>0.30865142</v>
       </c>
       <c r="N87">
-        <v>1.40493755</v>
+        <v>1.40134858</v>
       </c>
       <c r="O87">
-        <v>0.4917281425</v>
+        <v>0.490472003</v>
       </c>
       <c r="P87">
-        <v>0.9132094075000001</v>
+        <v>0.910876577</v>
       </c>
       <c r="Q87">
-        <v>1.0032094075</v>
+        <v>1.000876577</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8885305518194417</v>
+        <v>0.9442270295705996</v>
       </c>
       <c r="T87">
-        <v>4.140648852904079</v>
+        <v>4.414306377498655</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.605409646451079</v>
+        <v>5.540230464515601</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.163104484139884</v>
+        <v>0.1623761355068516</v>
       </c>
       <c r="C88">
-        <v>3.997136666890876</v>
+        <v>3.986908589166553</v>
       </c>
       <c r="D88">
-        <v>8.750536666890877</v>
+        <v>8.805208589166554</v>
       </c>
       <c r="E88">
-        <v>4.1314</v>
+        <v>4.1963</v>
       </c>
       <c r="F88">
-        <v>5.5814</v>
+        <v>5.6463</v>
       </c>
       <c r="G88">
         <v>0.828</v>
@@ -8616,28 +8616,28 @@
         <v>1.71</v>
       </c>
       <c r="M88">
-        <v>0.30865142</v>
+        <v>0.31224039</v>
       </c>
       <c r="N88">
-        <v>1.40134858</v>
+        <v>1.39775961</v>
       </c>
       <c r="O88">
-        <v>0.490472003</v>
+        <v>0.4892158635</v>
       </c>
       <c r="P88">
-        <v>0.910876577</v>
+        <v>0.9085437465000001</v>
       </c>
       <c r="Q88">
-        <v>1.000876577</v>
+        <v>0.9985437465</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.9442270295705996</v>
+        <v>1.008492196206551</v>
       </c>
       <c r="T88">
-        <v>4.414306377498655</v>
+        <v>4.730065059723165</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.540230464515601</v>
+        <v>5.476549654578641</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1623761355068516</v>
+        <v>0.1616477868738193</v>
       </c>
       <c r="C89">
-        <v>3.986908589166553</v>
+        <v>3.977367969026515</v>
       </c>
       <c r="D89">
-        <v>8.805208589166554</v>
+        <v>8.860567969026516</v>
       </c>
       <c r="E89">
-        <v>4.1963</v>
+        <v>4.2612</v>
       </c>
       <c r="F89">
-        <v>5.6463</v>
+        <v>5.7112</v>
       </c>
       <c r="G89">
         <v>0.828</v>
@@ -8698,28 +8698,28 @@
         <v>1.71</v>
       </c>
       <c r="M89">
-        <v>0.31224039</v>
+        <v>0.31582936</v>
       </c>
       <c r="N89">
-        <v>1.39775961</v>
+        <v>1.39417064</v>
       </c>
       <c r="O89">
-        <v>0.4892158635</v>
+        <v>0.487959724</v>
       </c>
       <c r="P89">
-        <v>0.9085437465000001</v>
+        <v>0.906210916</v>
       </c>
       <c r="Q89">
-        <v>0.9985437465</v>
+        <v>0.9962109159999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.008492196206551</v>
+        <v>1.083468223948494</v>
       </c>
       <c r="T89">
-        <v>4.730065059723165</v>
+        <v>5.098450188985095</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.476549654578641</v>
+        <v>5.414316135776611</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1616477868738193</v>
+        <v>0.160919438240787</v>
       </c>
       <c r="C90">
-        <v>3.977367969026515</v>
+        <v>3.968527854887252</v>
       </c>
       <c r="D90">
-        <v>8.860567969026516</v>
+        <v>8.916627854887253</v>
       </c>
       <c r="E90">
-        <v>4.2612</v>
+        <v>4.3261</v>
       </c>
       <c r="F90">
-        <v>5.7112</v>
+        <v>5.7761</v>
       </c>
       <c r="G90">
         <v>0.828</v>
@@ -8780,28 +8780,28 @@
         <v>1.71</v>
       </c>
       <c r="M90">
-        <v>0.31582936</v>
+        <v>0.31941833</v>
       </c>
       <c r="N90">
-        <v>1.39417064</v>
+        <v>1.39058167</v>
       </c>
       <c r="O90">
-        <v>0.487959724</v>
+        <v>0.4867035845</v>
       </c>
       <c r="P90">
-        <v>0.906210916</v>
+        <v>0.9038780855</v>
       </c>
       <c r="Q90">
-        <v>0.9962109159999999</v>
+        <v>0.9938780854999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.083468223948494</v>
+        <v>1.172076256734427</v>
       </c>
       <c r="T90">
-        <v>5.098450188985095</v>
+        <v>5.533814432658283</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.414316135776611</v>
+        <v>5.353481123015075</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.160919438240787</v>
+        <v>0.1601910896077547</v>
       </c>
       <c r="C91">
-        <v>3.968527854887252</v>
+        <v>3.960401627491692</v>
       </c>
       <c r="D91">
-        <v>8.916627854887253</v>
+        <v>8.973401627491693</v>
       </c>
       <c r="E91">
-        <v>4.3261</v>
+        <v>4.391</v>
       </c>
       <c r="F91">
-        <v>5.7761</v>
+        <v>5.841</v>
       </c>
       <c r="G91">
         <v>0.828</v>
@@ -8862,28 +8862,28 @@
         <v>1.71</v>
       </c>
       <c r="M91">
-        <v>0.31941833</v>
+        <v>0.3230073</v>
       </c>
       <c r="N91">
-        <v>1.39058167</v>
+        <v>1.3869927</v>
       </c>
       <c r="O91">
-        <v>0.4867035845</v>
+        <v>0.485447445</v>
       </c>
       <c r="P91">
-        <v>0.9038780855</v>
+        <v>0.901545255</v>
       </c>
       <c r="Q91">
-        <v>0.9938780854999999</v>
+        <v>0.9915452549999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.172076256734427</v>
+        <v>1.278405896077547</v>
       </c>
       <c r="T91">
-        <v>5.533814432658283</v>
+        <v>6.05625152506611</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.353481123015075</v>
+        <v>5.293997999426019</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1601910896077547</v>
+        <v>0.1594627409747223</v>
       </c>
       <c r="C92">
-        <v>3.960401627491692</v>
+        <v>3.953003010556943</v>
       </c>
       <c r="D92">
-        <v>8.973401627491693</v>
+        <v>9.030903010556944</v>
       </c>
       <c r="E92">
-        <v>4.391</v>
+        <v>4.455900000000001</v>
       </c>
       <c r="F92">
-        <v>5.841</v>
+        <v>5.905900000000001</v>
       </c>
       <c r="G92">
         <v>0.828</v>
@@ -8944,28 +8944,28 @@
         <v>1.71</v>
       </c>
       <c r="M92">
-        <v>0.3230073</v>
+        <v>0.3265962700000001</v>
       </c>
       <c r="N92">
-        <v>1.3869927</v>
+        <v>1.38340373</v>
       </c>
       <c r="O92">
-        <v>0.485447445</v>
+        <v>0.4841913054999999</v>
       </c>
       <c r="P92">
-        <v>0.901545255</v>
+        <v>0.8992124244999999</v>
       </c>
       <c r="Q92">
-        <v>0.9915452549999999</v>
+        <v>0.9892124244999998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.278405896077547</v>
+        <v>1.408364344163582</v>
       </c>
       <c r="T92">
-        <v>6.05625152506611</v>
+        <v>6.694785749120121</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.293997999426019</v>
+        <v>5.235822197234524</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1594627409747223</v>
+        <v>0.15873439234169</v>
       </c>
       <c r="C93">
-        <v>3.953003010556943</v>
+        <v>3.946346081833983</v>
       </c>
       <c r="D93">
-        <v>9.030903010556944</v>
+        <v>9.089146081833984</v>
       </c>
       <c r="E93">
-        <v>4.455900000000001</v>
+        <v>4.5208</v>
       </c>
       <c r="F93">
-        <v>5.905900000000001</v>
+        <v>5.970800000000001</v>
       </c>
       <c r="G93">
         <v>0.828</v>
@@ -9026,28 +9026,28 @@
         <v>1.71</v>
       </c>
       <c r="M93">
-        <v>0.3265962700000001</v>
+        <v>0.33018524</v>
       </c>
       <c r="N93">
-        <v>1.38340373</v>
+        <v>1.37981476</v>
       </c>
       <c r="O93">
-        <v>0.4841913054999999</v>
+        <v>0.4829351659999999</v>
       </c>
       <c r="P93">
-        <v>0.8992124244999999</v>
+        <v>0.8968795940000001</v>
       </c>
       <c r="Q93">
-        <v>0.9892124244999998</v>
+        <v>0.9868795939999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.408364344163582</v>
+        <v>1.570812404271126</v>
       </c>
       <c r="T93">
-        <v>6.694785749120121</v>
+        <v>7.492953529187635</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.235822197234524</v>
+        <v>5.178911086395018</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.15873439234169</v>
+        <v>0.1580060437086577</v>
       </c>
       <c r="C94">
-        <v>3.946346081833983</v>
+        <v>3.940445284598178</v>
       </c>
       <c r="D94">
-        <v>9.089146081833984</v>
+        <v>9.148145284598179</v>
       </c>
       <c r="E94">
-        <v>4.5208</v>
+        <v>4.5857</v>
       </c>
       <c r="F94">
-        <v>5.970800000000001</v>
+        <v>6.0357</v>
       </c>
       <c r="G94">
         <v>0.828</v>
@@ -9108,28 +9108,28 @@
         <v>1.71</v>
       </c>
       <c r="M94">
-        <v>0.33018524</v>
+        <v>0.33377421</v>
       </c>
       <c r="N94">
-        <v>1.37981476</v>
+        <v>1.37622579</v>
       </c>
       <c r="O94">
-        <v>0.4829351659999999</v>
+        <v>0.4816790264999999</v>
       </c>
       <c r="P94">
-        <v>0.8968795940000001</v>
+        <v>0.8945467635</v>
       </c>
       <c r="Q94">
-        <v>0.9868795939999999</v>
+        <v>0.9845467634999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.570812404271126</v>
+        <v>1.779674195837968</v>
       </c>
       <c r="T94">
-        <v>7.492953529187635</v>
+        <v>8.519169246417295</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.178911086395018</v>
+        <v>5.123223870412276</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1580060437086577</v>
+        <v>0.1572776950756253</v>
       </c>
       <c r="C95">
-        <v>3.940445284598178</v>
+        <v>3.935315439590153</v>
       </c>
       <c r="D95">
-        <v>9.148145284598179</v>
+        <v>9.207915439590154</v>
       </c>
       <c r="E95">
-        <v>4.5857</v>
+        <v>4.650600000000001</v>
       </c>
       <c r="F95">
-        <v>6.0357</v>
+        <v>6.100600000000001</v>
       </c>
       <c r="G95">
         <v>0.828</v>
@@ -9190,28 +9190,28 @@
         <v>1.71</v>
       </c>
       <c r="M95">
-        <v>0.33377421</v>
+        <v>0.33736318</v>
       </c>
       <c r="N95">
-        <v>1.37622579</v>
+        <v>1.37263682</v>
       </c>
       <c r="O95">
-        <v>0.4816790264999999</v>
+        <v>0.4804228869999999</v>
       </c>
       <c r="P95">
-        <v>0.8945467635</v>
+        <v>0.892213933</v>
       </c>
       <c r="Q95">
-        <v>0.9845467634999998</v>
+        <v>0.9822139329999998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.779674195837968</v>
+        <v>2.058156584593758</v>
       </c>
       <c r="T95">
-        <v>8.519169246417295</v>
+        <v>9.887456869390178</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.123223870412276</v>
+        <v>5.068721488812145</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1572776950756253</v>
+        <v>0.156549346442593</v>
       </c>
       <c r="C96">
-        <v>3.935315439590153</v>
+        <v>3.93097175742792</v>
       </c>
       <c r="D96">
-        <v>9.207915439590154</v>
+        <v>9.268471757427921</v>
       </c>
       <c r="E96">
-        <v>4.650600000000001</v>
+        <v>4.7155</v>
       </c>
       <c r="F96">
-        <v>6.100600000000001</v>
+        <v>6.165500000000001</v>
       </c>
       <c r="G96">
         <v>0.828</v>
@@ -9272,28 +9272,28 @@
         <v>1.71</v>
       </c>
       <c r="M96">
-        <v>0.33736318</v>
+        <v>0.3409521500000001</v>
       </c>
       <c r="N96">
-        <v>1.37263682</v>
+        <v>1.36904785</v>
       </c>
       <c r="O96">
-        <v>0.4804228869999999</v>
+        <v>0.4791667474999999</v>
       </c>
       <c r="P96">
-        <v>0.892213933</v>
+        <v>0.8898811025</v>
       </c>
       <c r="Q96">
-        <v>0.9822139329999998</v>
+        <v>0.9798811024999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.058156584593758</v>
+        <v>2.448031928851864</v>
       </c>
       <c r="T96">
-        <v>9.887456869390178</v>
+        <v>11.80305954155221</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.068721488812145</v>
+        <v>5.015366525772017</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.156549346442593</v>
+        <v>0.1558209978095607</v>
       </c>
       <c r="C97">
-        <v>3.93097175742792</v>
+        <v>3.927429851511982</v>
       </c>
       <c r="D97">
-        <v>9.268471757427921</v>
+        <v>9.329829851511983</v>
       </c>
       <c r="E97">
-        <v>4.7155</v>
+        <v>4.7804</v>
       </c>
       <c r="F97">
-        <v>6.165500000000001</v>
+        <v>6.2304</v>
       </c>
       <c r="G97">
         <v>0.828</v>
@@ -9354,28 +9354,28 @@
         <v>1.71</v>
       </c>
       <c r="M97">
-        <v>0.3409521500000001</v>
+        <v>0.34454112</v>
       </c>
       <c r="N97">
-        <v>1.36904785</v>
+        <v>1.36545888</v>
       </c>
       <c r="O97">
-        <v>0.4791667474999999</v>
+        <v>0.4779106079999999</v>
       </c>
       <c r="P97">
-        <v>0.8898811025</v>
+        <v>0.8875482719999999</v>
       </c>
       <c r="Q97">
-        <v>0.9798811024999998</v>
+        <v>0.9775482719999997</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.448031928851864</v>
+        <v>3.032844945239023</v>
       </c>
       <c r="T97">
-        <v>11.80305954155221</v>
+        <v>14.67646354979527</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.015366525772017</v>
+        <v>4.963123124461892</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1558209978095607</v>
+        <v>0.1550926491765284</v>
       </c>
       <c r="C98">
-        <v>3.92742985151198</v>
+        <v>3.924705751446449</v>
       </c>
       <c r="D98">
-        <v>9.329829851511981</v>
+        <v>9.392005751446449</v>
       </c>
       <c r="E98">
-        <v>4.7804</v>
+        <v>4.8453</v>
       </c>
       <c r="F98">
-        <v>6.2304</v>
+        <v>6.2953</v>
       </c>
       <c r="G98">
         <v>0.828</v>
@@ -9436,28 +9436,28 @@
         <v>1.71</v>
       </c>
       <c r="M98">
-        <v>0.34454112</v>
+        <v>0.34813009</v>
       </c>
       <c r="N98">
-        <v>1.36545888</v>
+        <v>1.36186991</v>
       </c>
       <c r="O98">
-        <v>0.4779106079999999</v>
+        <v>0.4766544685</v>
       </c>
       <c r="P98">
-        <v>0.8875482719999999</v>
+        <v>0.8852154415</v>
       </c>
       <c r="Q98">
-        <v>0.9775482719999997</v>
+        <v>0.9752154414999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.032844945239015</v>
+        <v>4.007533305884277</v>
       </c>
       <c r="T98">
-        <v>14.67646354979523</v>
+        <v>19.4654702302003</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.963123124461892</v>
+        <v>4.911956906683935</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1550926491765284</v>
+        <v>0.1543643005434961</v>
       </c>
       <c r="C99">
-        <v>3.924705751446449</v>
+        <v>3.92281591700043</v>
       </c>
       <c r="D99">
-        <v>9.392005751446449</v>
+        <v>9.455015917000431</v>
       </c>
       <c r="E99">
-        <v>4.8453</v>
+        <v>4.9102</v>
       </c>
       <c r="F99">
-        <v>6.2953</v>
+        <v>6.3602</v>
       </c>
       <c r="G99">
         <v>0.828</v>
@@ -9518,28 +9518,28 @@
         <v>1.71</v>
       </c>
       <c r="M99">
-        <v>0.34813009</v>
+        <v>0.35171906</v>
       </c>
       <c r="N99">
-        <v>1.36186991</v>
+        <v>1.35828094</v>
       </c>
       <c r="O99">
-        <v>0.4766544685</v>
+        <v>0.475398329</v>
       </c>
       <c r="P99">
-        <v>0.8852154415</v>
+        <v>0.8828826110000001</v>
       </c>
       <c r="Q99">
-        <v>0.9752154414999998</v>
+        <v>0.972882611</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.007533305884277</v>
+        <v>5.956910027174798</v>
       </c>
       <c r="T99">
-        <v>19.4654702302003</v>
+        <v>29.04348359101044</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.911956906683935</v>
+        <v>4.861834897432058</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1543643005434961</v>
+        <v>0.1536359519104638</v>
       </c>
       <c r="C100">
-        <v>3.92281591700043</v>
+        <v>3.921777252635172</v>
       </c>
       <c r="D100">
-        <v>9.455015917000431</v>
+        <v>9.518877252635173</v>
       </c>
       <c r="E100">
-        <v>4.9102</v>
+        <v>4.9751</v>
       </c>
       <c r="F100">
-        <v>6.3602</v>
+        <v>6.4251</v>
       </c>
       <c r="G100">
         <v>0.828</v>
@@ -9600,28 +9600,28 @@
         <v>1.71</v>
       </c>
       <c r="M100">
-        <v>0.35171906</v>
+        <v>0.3553080300000001</v>
       </c>
       <c r="N100">
-        <v>1.35828094</v>
+        <v>1.35469197</v>
       </c>
       <c r="O100">
-        <v>0.475398329</v>
+        <v>0.4741421895</v>
       </c>
       <c r="P100">
-        <v>0.8828826110000001</v>
+        <v>0.8805497805</v>
       </c>
       <c r="Q100">
-        <v>0.972882611</v>
+        <v>0.9705497804999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.956910027174798</v>
+        <v>11.80504019104636</v>
       </c>
       <c r="T100">
-        <v>29.04348359101044</v>
+        <v>57.77752367344086</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9638,91 +9638,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.861834897432058</v>
+        <v>4.812725454023653</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1536359519104638</v>
-      </c>
-      <c r="C101">
-        <v>3.921777252635172</v>
-      </c>
-      <c r="D101">
-        <v>9.518877252635173</v>
-      </c>
-      <c r="E101">
-        <v>4.9751</v>
-      </c>
-      <c r="F101">
-        <v>6.4251</v>
-      </c>
-      <c r="G101">
-        <v>0.828</v>
-      </c>
-      <c r="H101">
-        <v>5.04</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.8</v>
-      </c>
-      <c r="K101">
-        <v>0.08999999999999986</v>
-      </c>
-      <c r="L101">
-        <v>1.71</v>
-      </c>
-      <c r="M101">
-        <v>0.3553080300000001</v>
-      </c>
-      <c r="N101">
-        <v>1.35469197</v>
-      </c>
-      <c r="O101">
-        <v>0.4741421895</v>
-      </c>
-      <c r="P101">
-        <v>0.8805497805</v>
-      </c>
-      <c r="Q101">
-        <v>0.9705497804999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.80504019104636</v>
-      </c>
-      <c r="T101">
-        <v>57.77752367344086</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.035945</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.812725454023653</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
